--- a/data/data_replicated/4p_EFM/traces_references.xlsx
+++ b/data/data_replicated/4p_EFM/traces_references.xlsx
@@ -1,632 +1,625 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ituniversity-my.sharepoint.com/personal/kaib_itu_dk/Documents/Documents/GitHub/nonparamDNAmixtures/data/data_replicated/4p_EFM/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B89231273C59E19974D42389433E19D67A5E7916" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3646D6B-15FA-4546-ACB3-4B49454B5FE2}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-35670" yWindow="1560" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="200">
-  <si>
-    <t>trace</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
-    <t>EFM-A02-RD14-0003-40-41-42-43-1-1-1-1-M4I35-0124GF-QLAND-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>c40</t>
-  </si>
-  <si>
-    <t>c41</t>
-  </si>
-  <si>
-    <t>c42</t>
-  </si>
-  <si>
-    <t>c43</t>
-  </si>
-  <si>
-    <t>EFM-A02-RD14-0003-40-41-42-43-1-1-1-1-M4d-006GF-Q17-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A02-RD14-0003-50-29-30-31-1-1-2-1-M3c-0075GF-Q05-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>c29</t>
-  </si>
-  <si>
-    <t>c30</t>
-  </si>
-  <si>
-    <t>c31</t>
-  </si>
-  <si>
-    <t>c50</t>
-  </si>
-  <si>
-    <t>EFM-A03-RD14-0003-44-45-46-47-1-1-4-1-M2U105-0441GF-Q63-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>c44</t>
-  </si>
-  <si>
-    <t>c45</t>
-  </si>
-  <si>
-    <t>c46</t>
-  </si>
-  <si>
-    <t>c47</t>
-  </si>
-  <si>
-    <t>EFM-A03-RD14-0003-44-45-46-47-1-1-4-1-M3I35-0441GF-QLAND-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A03-RD14-0003-44-45-46-47-1-1-4-1-M3a-0105GF-Q08-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A03-RD14-0003-50-29-30-31-1-1-2-1-M3e-0075GF-Q11-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A04-RD14-0003-32-33-34-35-1-1-9-1-M2c-0372GF-Q04-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>c32</t>
-  </si>
-  <si>
-    <t>c33</t>
-  </si>
-  <si>
-    <t>c34</t>
-  </si>
-  <si>
-    <t>c35</t>
-  </si>
-  <si>
-    <t>EFM-A04-RD14-0003-44-45-46-47-1-1-4-1-M2e-0217GF-Q15-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A04-RD14-0003-48-49-50-29-1-4-4-4-M2U60-0403GF-Q49-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>c48</t>
-  </si>
-  <si>
-    <t>c49</t>
-  </si>
-  <si>
-    <t>EFM-A04-RD14-0003-48-49-50-29-1-4-4-4-M3I22-0403GF-Q17-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A05-RD14-0003-32-33-34-35-1-1-9-1-M2e-0372GF-Q06-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A05-RD14-0003-36-37-38-39-1-2-2-1-M3d-0186GF-Q12-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>c36</t>
-  </si>
-  <si>
-    <t>c37</t>
-  </si>
-  <si>
-    <t>c38</t>
-  </si>
-  <si>
-    <t>c39</t>
-  </si>
-  <si>
-    <t>EFM-A05-RD14-0003-40-41-42-43-1-1-1-1-M2S10-0124GF-Q13-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A06-RD14-0003-33-34-35-36-1-4-4-1-M2c-063GF-Q08-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A07-RD14-0003-33-34-35-36-1-4-4-1-M1e-063GF-Q12-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A08-RD14-0003-37-38-39-40-1-9-9-1-M2a-05GF-Q04-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A10-RD14-0003-48-49-50-29-1-4-4-4-M2a-05GF-Q04-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-A11-RD14-0003-48-49-50-29-1-4-4-4-M2d-05GF-Q07-0115sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B01-RD14-0003-40-41-42-43-1-1-1-1-M3I15-0252GF-Q16-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B01-RD14-0003-40-41-42-43-1-1-1-1-M3a-05GF-Q09-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B01-RD14-0003-50-29-30-31-1-1-2-1-M2a-0625GF-Q05-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B02-RD14-0003-40-41-42-43-1-1-1-1-M2e-05GF-Q32-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B02-RD14-0003-40-41-42-43-1-1-1-1-M3U105-006GF-QLAND-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B02-RD14-0003-40-41-42-43-1-1-1-1-M4I35-006GF-QLAND-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B02-RD14-0003-50-29-30-31-1-1-2-1-M2d-0625GF-Q08-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B04-RD14-0003-32-33-34-35-1-1-9-1-M2c-018GF-Q04-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B04-RD14-0003-44-45-46-47-1-1-4-1-M2e-0105GF-Q15-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B04-RD14-0003-48-49-50-29-1-4-4-4-M2U60-0195GF-Q49-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B04-RD14-0003-48-49-50-29-1-4-4-4-M3I22-0195GF-Q17-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B05-RD14-0003-32-33-34-35-1-1-9-1-M2e-018GF-Q06-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B05-RD14-0003-36-37-38-39-1-2-2-1-M3d-009GF-Q12-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B05-RD14-0003-40-41-42-43-1-1-1-1-M3S10-006GF-Q15-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B06-RD14-0003-33-34-35-36-1-4-4-1-M2c-031GF-Q08-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B07-RD14-0003-33-34-35-36-1-4-4-1-M1e-031GF-Q12-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B08-RD14-0003-37-38-39-40-1-9-9-1-M2a-03GF-Q04-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B09-RD14-0003-37-38-39-40-1-9-9-1-M2d-03GF-Q07-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B10-RD14-0003-48-49-50-29-1-4-4-4-M2a-0403GF-Q04-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-B11-RD14-0003-48-49-50-29-1-4-4-4-M2d-0403GF-Q07-0215sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C01-RD14-0003-40-41-42-43-1-1-1-1-M3a-0252GF-Q09-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C01-RD14-0003-40-41-42-43-1-1-1-1-M4I15-0124GF-Q16-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C01-RD14-0003-50-29-30-31-1-1-2-1-M2a-0315GF-Q05-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C02-RD14-0003-40-41-42-43-1-1-1-1-M2e-0252GF-Q32-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C02-RD14-0003-44-45-46-47-1-1-4-1-M2U15-0441GF-Q11-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C02-RD14-0003-44-45-46-47-1-1-4-1-M3I15-0441GF-Q11-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C02-RD14-0003-50-29-30-31-1-1-2-1-M2d-0315GF-Q08-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C03-RD14-0003-32-33-34-35-1-1-9-1-M2a-075GF-Q05-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C03-RD14-0003-44-45-46-47-1-1-4-1-M2U105-0217GF-Q63-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C03-RD14-0003-44-45-46-47-1-1-4-1-M2d-075GF-Q08-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C03-RD14-0003-44-45-46-47-1-1-4-1-M3I35-0217GF-QLAND-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C04-RD14-0003-32-33-34-35-1-1-9-1-M1d-075GF-Q06-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C04-RD14-0003-36-37-38-39-1-2-2-1-M1S30-075GF-Q26-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C04-RD14-0003-36-37-38-39-1-2-2-1-M2a-075GF-Q07-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C04-RD14-0003-48-49-50-29-1-4-4-4-M1U105-075GF-Q10-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C04-RD14-0003-48-49-50-29-1-4-4-4-M2I35-075GF-Q583-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C06-RD14-0003-33-34-35-36-1-4-4-1-M2c-015GF-Q08-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C07-RD14-0003-33-34-35-36-1-4-4-1-M2e-015GF-Q09-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C08-RD14-0003-37-38-39-40-1-9-9-1-M2c-075GF-Q06-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C10-RD14-0003-48-49-50-29-1-4-4-4-M3a-0195GF-Q04-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-C11-RD14-0003-48-49-50-29-1-4-4-4-M3d-0195GF-Q09-0315sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D01-RD14-0003-40-41-42-43-1-1-1-1-M3a-0124GF-Q09-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D01-RD14-0003-40-41-42-43-1-1-1-1-M4I15-006GF-Q16-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D01-RD14-0003-40-41-42-43-1-1-1-1-M4U15-006GF-Q37-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D01-RD14-0003-50-29-30-31-1-1-2-1-M2a-0155GF-Q05-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D02-RD14-0003-40-41-42-43-1-1-1-1-M2e-0124GF-Q32-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D02-RD14-0003-44-45-46-47-1-1-4-1-M2U15-0217GF-Q11-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D02-RD14-0003-44-45-46-47-1-1-4-1-M3I15-0217GF-Q11-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D02-RD14-0003-50-29-30-31-1-1-2-1-M2d-0155GF-Q08-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D03-RD14-0003-32-33-34-35-1-1-9-1-M2a-05GF-Q05-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D03-RD14-0003-44-45-46-47-1-1-4-1-M2U105-0105GF-Q63-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D03-RD14-0003-44-45-46-47-1-1-4-1-M2d-0441GF-Q08-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D03-RD14-0003-44-45-46-47-1-1-4-1-M3I35-0105GF-QLAND-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D04-RD14-0003-32-33-34-35-1-1-9-1-M1d-05GF-Q06-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D04-RD14-0003-36-37-38-39-1-2-2-1-M1S30-0378GF-Q26-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D04-RD14-0003-36-37-38-39-1-2-2-1-M2a-0378GF-Q07-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D04-RD14-0003-48-49-50-29-1-4-4-4-M1U105-0403GF-Q10-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D04-RD14-0003-48-49-50-29-1-4-4-4-M2I35-0403GF-Q583-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D05-RD14-0003-33-34-35-36-1-4-4-1-M2a-075GF-Q05-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D05-RD14-0003-36-37-38-39-1-2-2-1-M2e-075GF-Q12-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D05-RD14-0003-44-45-46-47-1-1-4-1-M1S30-075GF-Q29-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D08-RD14-0003-37-38-39-40-1-9-9-1-M2c-062GF-Q06-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D09-RD14-0003-37-38-39-40-1-9-9-1-M2e-062GF-Q08-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D10-RD14-0003-48-49-50-29-1-4-4-4-M2c-075GF-Q06-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-D11-RD14-0003-48-49-50-29-1-4-4-4-M1e-075GF-Q11-0415sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E01-RD14-0003-40-41-42-43-1-1-1-1-M2U60-0252GF-Q47-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E01-RD14-0003-40-41-42-43-1-1-1-1-M4I22-0252GF-Q35-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E01-RD14-0003-40-41-42-43-1-1-1-1-M4a-006GF-Q07-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E01-RD14-0003-50-29-30-31-1-1-2-1-M3a-0075GF-Q05-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E02-RD14-0003-40-41-42-43-1-1-1-1-M4e-006GF-Q56-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E02-RD14-0003-44-45-46-47-1-1-4-1-M3I15-0105GF-Q11-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E02-RD14-0003-44-45-46-47-1-1-4-1-M4U15-0105GF-Q44-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E02-RD14-0003-50-29-30-31-1-1-2-1-M4d-0075GF-Q12-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E03-RD14-0003-32-33-34-35-1-1-9-1-M2a-0372GF-Q05-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E03-RD14-0003-44-45-46-47-1-1-4-1-M2d-0217GF-Q08-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E03-RD14-0003-48-49-50-29-1-4-4-4-M2I15-075GF-Q11-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E03-RD14-0003-48-49-50-29-1-4-4-4-M2U15-075GF-Q13-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E04-RD14-0003-32-33-34-35-1-1-9-1-M2d-0372GF-Q05-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E04-RD14-0003-36-37-38-39-1-2-2-1-M2S30-0186GF-Q29-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E04-RD14-0003-36-37-38-39-1-2-2-1-M3a-0186GF-Q07-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E04-RD14-0003-48-49-50-29-1-4-4-4-M2U105-0195GF-Q121-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E04-RD14-0003-48-49-50-29-1-4-4-4-M4I35-0195GF-Q787-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E05-RD14-0003-33-34-35-36-1-4-4-1-M2a-063GF-Q05-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E05-RD14-0003-36-37-38-39-1-2-2-1-M2e-0378GF-Q12-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E05-RD14-0003-44-45-46-47-1-1-4-1-M1S30-0441GF-Q29-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E06-RD14-0003-33-34-35-36-1-4-4-1-M1d-063GF-Q09-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E08-RD14-0003-37-38-39-40-1-9-9-1-M2c-05GF-Q06-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E10-RD14-0003-48-49-50-29-1-4-4-4-M2c-05GF-Q06-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-E11-RD14-0003-48-49-50-29-1-4-4-4-M2e-05GF-Q13-0515sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F01-RD14-0003-40-41-42-43-1-1-1-1-M2U60-0124GF-Q47-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F01-RD14-0003-40-41-42-43-1-1-1-1-M2d-05GF-Q13-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F01-RD14-0003-40-41-42-43-1-1-1-1-M4I22-0124GF-Q35-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F01-RD14-0003-50-29-30-31-1-1-2-1-M2c-0625GF-Q06-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F02-RD14-0003-44-45-46-47-1-1-4-1-M2U60-0441GF-Q43-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F02-RD14-0003-44-45-46-47-1-1-4-1-M2a-075GF-Q07-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F02-RD14-0003-44-45-46-47-1-1-4-1-M3I22-0441GF-Q19-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F02-RD14-0003-50-29-30-31-1-1-2-1-M1e-0625GF-Q09-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F03-RD14-0003-32-33-34-35-1-1-9-1-M2a-018GF-Q05-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F03-RD14-0003-44-45-46-47-1-1-4-1-M3d-0105GF-Q08-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F03-RD14-0003-48-49-50-29-1-4-4-4-M2I15-0403GF-Q11-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F03-RD14-0003-48-49-50-29-1-4-4-4-M2U15-0403GF-Q13-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F04-RD14-0003-32-33-34-35-1-1-9-1-M2d-018GF-Q05-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F04-RD14-0003-36-37-38-39-1-2-2-1-M2S30-009GF-Q29-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F04-RD14-0003-36-37-38-39-1-2-2-1-M3a-009GF-Q07-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F05-RD14-0003-33-34-35-36-1-4-4-1-M2a-031GF-Q05-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F05-RD14-0003-36-37-38-39-1-2-2-1-M2e-0186GF-Q12-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F05-RD14-0003-44-45-46-47-1-1-4-1-M2S30-0217GF-Q33-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F06-RD14-0003-33-34-35-36-1-4-4-1-M2d-031GF-Q09-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F08-RD14-0003-37-38-39-40-1-9-9-1-M2c-03GF-Q06-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F09-RD14-0003-37-38-39-40-1-9-9-1-M2e-05GF-Q08-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-F10-RD14-0003-48-49-50-29-1-4-4-4-M2c-0403GF-Q06-0615sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G01-RD14-0003-40-41-42-43-1-1-1-1-M2d-0252GF-Q13-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G01-RD14-0003-40-41-42-43-1-1-1-1-M3U60-006GF-Q388-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G01-RD14-0003-40-41-42-43-1-1-1-1-M4I22-006GF-Q35-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G01-RD14-0003-50-29-30-31-1-1-2-1-M2c-0315GF-Q06-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G02-RD14-0003-44-45-46-47-1-1-4-1-M2U60-0217GF-Q43-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G02-RD14-0003-44-45-46-47-1-1-4-1-M2a-0441GF-Q07-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G02-RD14-0003-44-45-46-47-1-1-4-1-M3I22-0217GF-Q19-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G02-RD14-0003-50-29-30-31-1-1-2-1-M2e-0315GF-Q10-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G03-RD14-0003-32-33-34-35-1-1-9-1-M1c-075GF-Q05-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G03-RD14-0003-44-45-46-47-1-1-4-1-M2e-075GF-Q15-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G03-RD14-0003-48-49-50-29-1-4-4-4-M3I15-0195GF-Q11-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G03-RD14-0003-48-49-50-29-1-4-4-4-M3U15-0195GF-Q15-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G04-RD14-0003-32-33-34-35-1-1-9-1-M1e-075GF-Q07-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G04-RD14-0003-36-37-38-39-1-2-2-1-M2d-075GF-Q08-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G04-RD14-0003-40-41-42-43-1-1-1-1-M1S10-05GF-Q13-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G05-RD14-0003-33-34-35-36-1-4-4-1-M2a-015GF-Q05-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G05-RD14-0003-36-37-38-39-1-2-2-1-M3e-009GF-Q12-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G05-RD14-0003-44-45-46-47-1-1-4-1-M2S30-0105GF-Q33-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G06-RD14-0003-33-34-35-36-1-4-4-1-M2d-015GF-Q09-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G07-RD14-0003-37-38-39-40-1-9-9-1-M2a-075GF-Q04-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G08-RD14-0003-37-38-39-40-1-9-9-1-M2d-075GF-Q07-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G09-RD14-0003-37-38-39-40-1-9-9-1-M2e-03GF-Q08-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G10-RD14-0003-48-49-50-29-1-4-4-4-M3c-0195GF-Q11-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-G11-RD14-0003-48-49-50-29-1-4-4-4-M2e-0403GF-Q13-0715sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H01-RD14-0003-40-41-42-43-1-1-1-1-M2U105-0252GF-Q12-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H01-RD14-0003-40-41-42-43-1-1-1-1-M4I35-0252GF-QLAND-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H01-RD14-0003-40-41-42-43-1-1-1-1-M4d-0124GF-Q17-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H01-RD14-0003-50-29-30-31-1-1-2-1-M2c-0155GF-Q06-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H02-RD14-0003-44-45-46-47-1-1-4-1-M3I22-0105GF-Q19-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H02-RD14-0003-44-45-46-47-1-1-4-1-M3U60-0105GF-Q287-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H02-RD14-0003-44-45-46-47-1-1-4-1-M3a-0217GF-Q08-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H02-RD14-0003-50-29-30-31-1-1-2-1-M2e-0155GF-Q10-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H03-RD14-0003-32-33-34-35-1-1-9-1-M2c-05GF-Q04-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H03-RD14-0003-44-45-46-47-1-1-4-1-M2e-0441GF-Q15-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H03-RD14-0003-48-49-50-29-1-4-4-4-M1U60-075GF-Q10-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H03-RD14-0003-48-49-50-29-1-4-4-4-M3I22-075GF-Q17-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H04-RD14-0003-32-33-34-35-1-1-9-1-M1e-05GF-Q07-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H04-RD14-0003-36-37-38-39-1-2-2-1-M2d-0378GF-Q08-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H04-RD14-0003-40-41-42-43-1-1-1-1-M2S10-0252GF-Q13-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H05-RD14-0003-33-34-35-36-1-4-4-1-M1c-075GF-Q07-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H06-RD14-0003-33-34-35-36-1-4-4-1-M1e-075GF-Q12-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H07-RD14-0003-37-38-39-40-1-9-9-1-M2a-062GF-Q04-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H08-RD14-0003-37-38-39-40-1-9-9-1-M2d-062GF-Q07-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H09-RD14-0003-48-49-50-29-1-4-4-4-M2a-075GF-Q04-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H10-RD14-0003-48-49-50-29-1-4-4-4-M2d-075GF-Q07-0815sechid.csv</t>
-  </si>
-  <si>
-    <t>EFM-H11-RD14-0003-48-49-50-29-1-4-4-4-M2e-0195GF-Q13-0815sechid.csv</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+  <si>
+    <t xml:space="preserve">trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A02-RD14-0003-40-41-42-43-1-1-1-1-M4I35-0124GF-QLAND-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A02-RD14-0003-40-41-42-43-1-1-1-1-M4d-006GF-Q17-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A02-RD14-0003-50-29-30-31-1-1-2-1-M3c-0075GF-Q05-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A03-RD14-0003-44-45-46-47-1-1-4-1-M2U105-0441GF-Q63-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A03-RD14-0003-44-45-46-47-1-1-4-1-M3I35-0441GF-QLAND-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A03-RD14-0003-44-45-46-47-1-1-4-1-M3a-0105GF-Q08-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A03-RD14-0003-50-29-30-31-1-1-2-1-M3e-0075GF-Q11-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A04-RD14-0003-32-33-34-35-1-1-9-1-M2c-0372GF-Q04-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A04-RD14-0003-44-45-46-47-1-1-4-1-M2e-0217GF-Q15-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A04-RD14-0003-48-49-50-29-1-4-4-4-M2U60-0403GF-Q49-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A04-RD14-0003-48-49-50-29-1-4-4-4-M3I22-0403GF-Q17-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A05-RD14-0003-32-33-34-35-1-1-9-1-M2e-0372GF-Q06-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A05-RD14-0003-36-37-38-39-1-2-2-1-M3d-0186GF-Q12-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A05-RD14-0003-40-41-42-43-1-1-1-1-M2S10-0124GF-Q13-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A06-RD14-0003-33-34-35-36-1-4-4-1-M2c-063GF-Q08-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A07-RD14-0003-33-34-35-36-1-4-4-1-M1e-063GF-Q12-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A08-RD14-0003-37-38-39-40-1-9-9-1-M2a-05GF-Q04-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A10-RD14-0003-48-49-50-29-1-4-4-4-M2a-05GF-Q04-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-A11-RD14-0003-48-49-50-29-1-4-4-4-M2d-05GF-Q07-0115sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B01-RD14-0003-40-41-42-43-1-1-1-1-M3I15-0252GF-Q16-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B01-RD14-0003-40-41-42-43-1-1-1-1-M3a-05GF-Q09-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B01-RD14-0003-50-29-30-31-1-1-2-1-M2a-0625GF-Q05-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B02-RD14-0003-40-41-42-43-1-1-1-1-M2e-05GF-Q32-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B02-RD14-0003-40-41-42-43-1-1-1-1-M3U105-006GF-QLAND-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B02-RD14-0003-40-41-42-43-1-1-1-1-M4I35-006GF-QLAND-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B02-RD14-0003-50-29-30-31-1-1-2-1-M2d-0625GF-Q08-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B04-RD14-0003-32-33-34-35-1-1-9-1-M2c-018GF-Q04-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B04-RD14-0003-44-45-46-47-1-1-4-1-M2e-0105GF-Q15-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B04-RD14-0003-48-49-50-29-1-4-4-4-M2U60-0195GF-Q49-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B04-RD14-0003-48-49-50-29-1-4-4-4-M3I22-0195GF-Q17-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B05-RD14-0003-32-33-34-35-1-1-9-1-M2e-018GF-Q06-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B05-RD14-0003-36-37-38-39-1-2-2-1-M3d-009GF-Q12-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B05-RD14-0003-40-41-42-43-1-1-1-1-M3S10-006GF-Q15-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B06-RD14-0003-33-34-35-36-1-4-4-1-M2c-031GF-Q08-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B07-RD14-0003-33-34-35-36-1-4-4-1-M1e-031GF-Q12-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B08-RD14-0003-37-38-39-40-1-9-9-1-M2a-03GF-Q04-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B09-RD14-0003-37-38-39-40-1-9-9-1-M2d-03GF-Q07-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B10-RD14-0003-48-49-50-29-1-4-4-4-M2a-0403GF-Q04-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-B11-RD14-0003-48-49-50-29-1-4-4-4-M2d-0403GF-Q07-0215sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C01-RD14-0003-40-41-42-43-1-1-1-1-M3a-0252GF-Q09-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C01-RD14-0003-40-41-42-43-1-1-1-1-M4I15-0124GF-Q16-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C01-RD14-0003-50-29-30-31-1-1-2-1-M2a-0315GF-Q05-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C02-RD14-0003-40-41-42-43-1-1-1-1-M2e-0252GF-Q32-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C02-RD14-0003-44-45-46-47-1-1-4-1-M2U15-0441GF-Q11-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C02-RD14-0003-44-45-46-47-1-1-4-1-M3I15-0441GF-Q11-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C02-RD14-0003-50-29-30-31-1-1-2-1-M2d-0315GF-Q08-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C03-RD14-0003-32-33-34-35-1-1-9-1-M2a-075GF-Q05-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C03-RD14-0003-44-45-46-47-1-1-4-1-M2U105-0217GF-Q63-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C03-RD14-0003-44-45-46-47-1-1-4-1-M2d-075GF-Q08-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C03-RD14-0003-44-45-46-47-1-1-4-1-M3I35-0217GF-QLAND-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C04-RD14-0003-32-33-34-35-1-1-9-1-M1d-075GF-Q06-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C04-RD14-0003-36-37-38-39-1-2-2-1-M1S30-075GF-Q26-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C04-RD14-0003-36-37-38-39-1-2-2-1-M2a-075GF-Q07-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C04-RD14-0003-48-49-50-29-1-4-4-4-M1U105-075GF-Q10-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C04-RD14-0003-48-49-50-29-1-4-4-4-M2I35-075GF-Q583-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C06-RD14-0003-33-34-35-36-1-4-4-1-M2c-015GF-Q08-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C07-RD14-0003-33-34-35-36-1-4-4-1-M2e-015GF-Q09-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C08-RD14-0003-37-38-39-40-1-9-9-1-M2c-075GF-Q06-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C10-RD14-0003-48-49-50-29-1-4-4-4-M3a-0195GF-Q04-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-C11-RD14-0003-48-49-50-29-1-4-4-4-M3d-0195GF-Q09-0315sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D01-RD14-0003-40-41-42-43-1-1-1-1-M3a-0124GF-Q09-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D01-RD14-0003-40-41-42-43-1-1-1-1-M4I15-006GF-Q16-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D01-RD14-0003-40-41-42-43-1-1-1-1-M4U15-006GF-Q37-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D01-RD14-0003-50-29-30-31-1-1-2-1-M2a-0155GF-Q05-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D02-RD14-0003-40-41-42-43-1-1-1-1-M2e-0124GF-Q32-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D02-RD14-0003-44-45-46-47-1-1-4-1-M2U15-0217GF-Q11-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D02-RD14-0003-44-45-46-47-1-1-4-1-M3I15-0217GF-Q11-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D02-RD14-0003-50-29-30-31-1-1-2-1-M2d-0155GF-Q08-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D03-RD14-0003-32-33-34-35-1-1-9-1-M2a-05GF-Q05-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D03-RD14-0003-44-45-46-47-1-1-4-1-M2U105-0105GF-Q63-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D03-RD14-0003-44-45-46-47-1-1-4-1-M2d-0441GF-Q08-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D03-RD14-0003-44-45-46-47-1-1-4-1-M3I35-0105GF-QLAND-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D04-RD14-0003-32-33-34-35-1-1-9-1-M1d-05GF-Q06-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D04-RD14-0003-36-37-38-39-1-2-2-1-M1S30-0378GF-Q26-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D04-RD14-0003-36-37-38-39-1-2-2-1-M2a-0378GF-Q07-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D04-RD14-0003-48-49-50-29-1-4-4-4-M1U105-0403GF-Q10-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D04-RD14-0003-48-49-50-29-1-4-4-4-M2I35-0403GF-Q583-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D05-RD14-0003-33-34-35-36-1-4-4-1-M2a-075GF-Q05-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D05-RD14-0003-36-37-38-39-1-2-2-1-M2e-075GF-Q12-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D05-RD14-0003-44-45-46-47-1-1-4-1-M1S30-075GF-Q29-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D08-RD14-0003-37-38-39-40-1-9-9-1-M2c-062GF-Q06-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D09-RD14-0003-37-38-39-40-1-9-9-1-M2e-062GF-Q08-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D10-RD14-0003-48-49-50-29-1-4-4-4-M2c-075GF-Q06-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-D11-RD14-0003-48-49-50-29-1-4-4-4-M1e-075GF-Q11-0415sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E01-RD14-0003-40-41-42-43-1-1-1-1-M2U60-0252GF-Q47-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E01-RD14-0003-40-41-42-43-1-1-1-1-M4I22-0252GF-Q35-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E01-RD14-0003-40-41-42-43-1-1-1-1-M4a-006GF-Q07-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E01-RD14-0003-50-29-30-31-1-1-2-1-M3a-0075GF-Q05-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E02-RD14-0003-40-41-42-43-1-1-1-1-M4e-006GF-Q56-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E02-RD14-0003-44-45-46-47-1-1-4-1-M3I15-0105GF-Q11-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E02-RD14-0003-44-45-46-47-1-1-4-1-M4U15-0105GF-Q44-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E02-RD14-0003-50-29-30-31-1-1-2-1-M4d-0075GF-Q12-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E03-RD14-0003-32-33-34-35-1-1-9-1-M2a-0372GF-Q05-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E03-RD14-0003-44-45-46-47-1-1-4-1-M2d-0217GF-Q08-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E03-RD14-0003-48-49-50-29-1-4-4-4-M2I15-075GF-Q11-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E03-RD14-0003-48-49-50-29-1-4-4-4-M2U15-075GF-Q13-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E04-RD14-0003-32-33-34-35-1-1-9-1-M2d-0372GF-Q05-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E04-RD14-0003-36-37-38-39-1-2-2-1-M2S30-0186GF-Q29-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E04-RD14-0003-36-37-38-39-1-2-2-1-M3a-0186GF-Q07-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E04-RD14-0003-48-49-50-29-1-4-4-4-M2U105-0195GF-Q121-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E04-RD14-0003-48-49-50-29-1-4-4-4-M4I35-0195GF-Q787-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E05-RD14-0003-33-34-35-36-1-4-4-1-M2a-063GF-Q05-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E05-RD14-0003-36-37-38-39-1-2-2-1-M2e-0378GF-Q12-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E05-RD14-0003-44-45-46-47-1-1-4-1-M1S30-0441GF-Q29-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E06-RD14-0003-33-34-35-36-1-4-4-1-M1d-063GF-Q09-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E08-RD14-0003-37-38-39-40-1-9-9-1-M2c-05GF-Q06-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E10-RD14-0003-48-49-50-29-1-4-4-4-M2c-05GF-Q06-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-E11-RD14-0003-48-49-50-29-1-4-4-4-M2e-05GF-Q13-0515sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F01-RD14-0003-40-41-42-43-1-1-1-1-M2U60-0124GF-Q47-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F01-RD14-0003-40-41-42-43-1-1-1-1-M2d-05GF-Q13-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F01-RD14-0003-40-41-42-43-1-1-1-1-M4I22-0124GF-Q35-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F01-RD14-0003-50-29-30-31-1-1-2-1-M2c-0625GF-Q06-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F02-RD14-0003-44-45-46-47-1-1-4-1-M2U60-0441GF-Q43-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F02-RD14-0003-44-45-46-47-1-1-4-1-M2a-075GF-Q07-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F02-RD14-0003-44-45-46-47-1-1-4-1-M3I22-0441GF-Q19-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F02-RD14-0003-50-29-30-31-1-1-2-1-M1e-0625GF-Q09-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F03-RD14-0003-32-33-34-35-1-1-9-1-M2a-018GF-Q05-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F03-RD14-0003-44-45-46-47-1-1-4-1-M3d-0105GF-Q08-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F03-RD14-0003-48-49-50-29-1-4-4-4-M2I15-0403GF-Q11-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F03-RD14-0003-48-49-50-29-1-4-4-4-M2U15-0403GF-Q13-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F04-RD14-0003-32-33-34-35-1-1-9-1-M2d-018GF-Q05-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F04-RD14-0003-36-37-38-39-1-2-2-1-M2S30-009GF-Q29-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F04-RD14-0003-36-37-38-39-1-2-2-1-M3a-009GF-Q07-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F05-RD14-0003-33-34-35-36-1-4-4-1-M2a-031GF-Q05-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F05-RD14-0003-36-37-38-39-1-2-2-1-M2e-0186GF-Q12-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F05-RD14-0003-44-45-46-47-1-1-4-1-M2S30-0217GF-Q33-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F06-RD14-0003-33-34-35-36-1-4-4-1-M2d-031GF-Q09-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F08-RD14-0003-37-38-39-40-1-9-9-1-M2c-03GF-Q06-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F09-RD14-0003-37-38-39-40-1-9-9-1-M2e-05GF-Q08-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-F10-RD14-0003-48-49-50-29-1-4-4-4-M2c-0403GF-Q06-0615sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G01-RD14-0003-40-41-42-43-1-1-1-1-M2d-0252GF-Q13-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G01-RD14-0003-40-41-42-43-1-1-1-1-M3U60-006GF-Q388-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G01-RD14-0003-40-41-42-43-1-1-1-1-M4I22-006GF-Q35-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G01-RD14-0003-50-29-30-31-1-1-2-1-M2c-0315GF-Q06-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G02-RD14-0003-44-45-46-47-1-1-4-1-M2U60-0217GF-Q43-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G02-RD14-0003-44-45-46-47-1-1-4-1-M2a-0441GF-Q07-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G02-RD14-0003-44-45-46-47-1-1-4-1-M3I22-0217GF-Q19-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G02-RD14-0003-50-29-30-31-1-1-2-1-M2e-0315GF-Q10-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G03-RD14-0003-32-33-34-35-1-1-9-1-M1c-075GF-Q05-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G03-RD14-0003-44-45-46-47-1-1-4-1-M2e-075GF-Q15-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G03-RD14-0003-48-49-50-29-1-4-4-4-M3I15-0195GF-Q11-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G03-RD14-0003-48-49-50-29-1-4-4-4-M3U15-0195GF-Q15-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G04-RD14-0003-32-33-34-35-1-1-9-1-M1e-075GF-Q07-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G04-RD14-0003-36-37-38-39-1-2-2-1-M2d-075GF-Q08-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G04-RD14-0003-40-41-42-43-1-1-1-1-M1S10-05GF-Q13-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G05-RD14-0003-33-34-35-36-1-4-4-1-M2a-015GF-Q05-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G05-RD14-0003-36-37-38-39-1-2-2-1-M3e-009GF-Q12-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G05-RD14-0003-44-45-46-47-1-1-4-1-M2S30-0105GF-Q33-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G06-RD14-0003-33-34-35-36-1-4-4-1-M2d-015GF-Q09-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G07-RD14-0003-37-38-39-40-1-9-9-1-M2a-075GF-Q04-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G08-RD14-0003-37-38-39-40-1-9-9-1-M2d-075GF-Q07-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G09-RD14-0003-37-38-39-40-1-9-9-1-M2e-03GF-Q08-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G10-RD14-0003-48-49-50-29-1-4-4-4-M3c-0195GF-Q11-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-G11-RD14-0003-48-49-50-29-1-4-4-4-M2e-0403GF-Q13-0715sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H01-RD14-0003-40-41-42-43-1-1-1-1-M2U105-0252GF-Q12-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H01-RD14-0003-40-41-42-43-1-1-1-1-M4I35-0252GF-QLAND-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H01-RD14-0003-40-41-42-43-1-1-1-1-M4d-0124GF-Q17-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H01-RD14-0003-50-29-30-31-1-1-2-1-M2c-0155GF-Q06-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H02-RD14-0003-44-45-46-47-1-1-4-1-M3I22-0105GF-Q19-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H02-RD14-0003-44-45-46-47-1-1-4-1-M3U60-0105GF-Q287-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H02-RD14-0003-44-45-46-47-1-1-4-1-M3a-0217GF-Q08-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H02-RD14-0003-50-29-30-31-1-1-2-1-M2e-0155GF-Q10-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H03-RD14-0003-32-33-34-35-1-1-9-1-M2c-05GF-Q04-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H03-RD14-0003-44-45-46-47-1-1-4-1-M2e-0441GF-Q15-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H03-RD14-0003-48-49-50-29-1-4-4-4-M1U60-075GF-Q10-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H03-RD14-0003-48-49-50-29-1-4-4-4-M3I22-075GF-Q17-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H04-RD14-0003-32-33-34-35-1-1-9-1-M1e-05GF-Q07-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H04-RD14-0003-36-37-38-39-1-2-2-1-M2d-0378GF-Q08-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H04-RD14-0003-40-41-42-43-1-1-1-1-M2S10-0252GF-Q13-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H05-RD14-0003-33-34-35-36-1-4-4-1-M1c-075GF-Q07-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H06-RD14-0003-33-34-35-36-1-4-4-1-M1e-075GF-Q12-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H07-RD14-0003-37-38-39-40-1-9-9-1-M2a-062GF-Q04-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H08-RD14-0003-37-38-39-40-1-9-9-1-M2d-062GF-Q07-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H09-RD14-0003-48-49-50-29-1-4-4-4-M2a-075GF-Q04-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H10-RD14-0003-48-49-50-29-1-4-4-4-M2d-075GF-Q07-0815sechid.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFM-H11-RD14-0003-48-49-50-29-1-4-4-4-M2e-0195GF-Q13-0815sechid.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -662,15 +655,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -952,14 +936,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B705"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="72.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -967,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -975,7 +956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -983,7 +964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -991,7 +972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -999,7 +980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1007,7 +988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1015,7 +996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1023,7 +1004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1031,7 +1012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1039,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1047,7 +1028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1055,7 +1036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1063,7 +1044,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1071,7 +1052,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1079,7 +1060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1087,7 +1068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1095,7 +1076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1103,7 +1084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1111,7 +1092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1119,7 +1100,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1127,7 +1108,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1135,7 +1116,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1143,7 +1124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1151,7 +1132,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -1159,7 +1140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1167,7 +1148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1175,7 +1156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -1183,7 +1164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -1191,7 +1172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -1199,7 +1180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -1207,7 +1188,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -1215,7 +1196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -1223,7 +1204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -1231,7 +1212,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -1239,7 +1220,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -1247,7 +1228,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -1255,7 +1236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1263,7 +1244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1271,7 +1252,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1279,7 +1260,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1268,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>30</v>
       </c>
@@ -1295,7 +1276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -1303,7 +1284,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>30</v>
       </c>
@@ -1311,7 +1292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -1319,7 +1300,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>31</v>
       </c>
@@ -1327,7 +1308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>31</v>
       </c>
@@ -1335,7 +1316,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>31</v>
       </c>
@@ -1343,7 +1324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>31</v>
       </c>
@@ -1351,7 +1332,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>32</v>
       </c>
@@ -1359,7 +1340,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1367,7 +1348,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -1375,7 +1356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>32</v>
       </c>
@@ -1383,7 +1364,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>37</v>
       </c>
@@ -1391,7 +1372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>37</v>
       </c>
@@ -1399,7 +1380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>37</v>
       </c>
@@ -1407,7 +1388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -1415,7 +1396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>38</v>
       </c>
@@ -1423,7 +1404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>38</v>
       </c>
@@ -1431,7 +1412,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>38</v>
       </c>
@@ -1439,7 +1420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>38</v>
       </c>
@@ -1447,7 +1428,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>39</v>
       </c>
@@ -1455,7 +1436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -1463,7 +1444,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -1471,7 +1452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -1479,7 +1460,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -1487,7 +1468,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -1495,7 +1476,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -1503,7 +1484,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -1511,7 +1492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>41</v>
       </c>
@@ -1519,7 +1500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>41</v>
       </c>
@@ -1527,7 +1508,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>41</v>
       </c>
@@ -1535,7 +1516,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>41</v>
       </c>
@@ -1543,7 +1524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>42</v>
       </c>
@@ -1551,7 +1532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>42</v>
       </c>
@@ -1559,7 +1540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>42</v>
       </c>
@@ -1567,7 +1548,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>42</v>
       </c>
@@ -1575,7 +1556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>43</v>
       </c>
@@ -1583,7 +1564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>43</v>
       </c>
@@ -1591,7 +1572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>43</v>
       </c>
@@ -1599,7 +1580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>43</v>
       </c>
@@ -1607,7 +1588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>44</v>
       </c>
@@ -1615,7 +1596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>44</v>
       </c>
@@ -1623,7 +1604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -1631,7 +1612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>44</v>
       </c>
@@ -1639,7 +1620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>45</v>
       </c>
@@ -1647,7 +1628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" t="s">
         <v>45</v>
       </c>
@@ -1655,7 +1636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88" t="s">
         <v>45</v>
       </c>
@@ -1663,7 +1644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" t="s">
         <v>45</v>
       </c>
@@ -1671,7 +1652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90" t="s">
         <v>46</v>
       </c>
@@ -1679,7 +1660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91" t="s">
         <v>46</v>
       </c>
@@ -1687,7 +1668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" t="s">
         <v>46</v>
       </c>
@@ -1695,7 +1676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" t="s">
         <v>46</v>
       </c>
@@ -1703,7 +1684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94" t="s">
         <v>47</v>
       </c>
@@ -1711,7 +1692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -1719,7 +1700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" t="s">
         <v>47</v>
       </c>
@@ -1727,7 +1708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>47</v>
       </c>
@@ -1735,7 +1716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>48</v>
       </c>
@@ -1743,7 +1724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99" t="s">
         <v>48</v>
       </c>
@@ -1751,7 +1732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>48</v>
       </c>
@@ -1759,7 +1740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101" t="s">
         <v>48</v>
       </c>
@@ -1767,7 +1748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="A102" t="s">
         <v>49</v>
       </c>
@@ -1775,7 +1756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="A103" t="s">
         <v>49</v>
       </c>
@@ -1783,7 +1764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="A104" t="s">
         <v>49</v>
       </c>
@@ -1791,7 +1772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="A105" t="s">
         <v>49</v>
       </c>
@@ -1799,7 +1780,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="A106" t="s">
         <v>50</v>
       </c>
@@ -1807,7 +1788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="A107" t="s">
         <v>50</v>
       </c>
@@ -1815,7 +1796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="A108" t="s">
         <v>50</v>
       </c>
@@ -1823,7 +1804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="A109" t="s">
         <v>50</v>
       </c>
@@ -1831,7 +1812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="A110" t="s">
         <v>51</v>
       </c>
@@ -1839,7 +1820,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="A111" t="s">
         <v>51</v>
       </c>
@@ -1847,7 +1828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="A112" t="s">
         <v>51</v>
       </c>
@@ -1855,7 +1836,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="A113" t="s">
         <v>51</v>
       </c>
@@ -1863,7 +1844,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="A114" t="s">
         <v>52</v>
       </c>
@@ -1871,7 +1852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="A115" t="s">
         <v>52</v>
       </c>
@@ -1879,7 +1860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116">
       <c r="A116" t="s">
         <v>52</v>
       </c>
@@ -1887,7 +1868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117">
       <c r="A117" t="s">
         <v>52</v>
       </c>
@@ -1895,7 +1876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118">
       <c r="A118" t="s">
         <v>53</v>
       </c>
@@ -1903,7 +1884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -1911,7 +1892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120">
       <c r="A120" t="s">
         <v>53</v>
       </c>
@@ -1919,7 +1900,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121">
       <c r="A121" t="s">
         <v>53</v>
       </c>
@@ -1927,7 +1908,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122">
       <c r="A122" t="s">
         <v>54</v>
       </c>
@@ -1935,7 +1916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="A123" t="s">
         <v>54</v>
       </c>
@@ -1943,7 +1924,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124">
       <c r="A124" t="s">
         <v>54</v>
       </c>
@@ -1951,7 +1932,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125">
       <c r="A125" t="s">
         <v>54</v>
       </c>
@@ -1959,7 +1940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126">
       <c r="A126" t="s">
         <v>55</v>
       </c>
@@ -1967,7 +1948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127">
       <c r="A127" t="s">
         <v>55</v>
       </c>
@@ -1975,7 +1956,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128">
       <c r="A128" t="s">
         <v>55</v>
       </c>
@@ -1983,7 +1964,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129">
       <c r="A129" t="s">
         <v>55</v>
       </c>
@@ -1991,7 +1972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130">
       <c r="A130" t="s">
         <v>56</v>
       </c>
@@ -1999,7 +1980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131">
       <c r="A131" t="s">
         <v>56</v>
       </c>
@@ -2007,7 +1988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132">
       <c r="A132" t="s">
         <v>56</v>
       </c>
@@ -2015,7 +1996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133">
       <c r="A133" t="s">
         <v>56</v>
       </c>
@@ -2023,7 +2004,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134">
       <c r="A134" t="s">
         <v>57</v>
       </c>
@@ -2031,7 +2012,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135">
       <c r="A135" t="s">
         <v>57</v>
       </c>
@@ -2039,7 +2020,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136">
       <c r="A136" t="s">
         <v>57</v>
       </c>
@@ -2047,7 +2028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137">
       <c r="A137" t="s">
         <v>57</v>
       </c>
@@ -2055,7 +2036,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138">
       <c r="A138" t="s">
         <v>58</v>
       </c>
@@ -2063,7 +2044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139">
       <c r="A139" t="s">
         <v>58</v>
       </c>
@@ -2071,7 +2052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140">
       <c r="A140" t="s">
         <v>58</v>
       </c>
@@ -2079,7 +2060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141">
       <c r="A141" t="s">
         <v>58</v>
       </c>
@@ -2087,7 +2068,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142">
       <c r="A142" t="s">
         <v>59</v>
       </c>
@@ -2095,7 +2076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143">
       <c r="A143" t="s">
         <v>59</v>
       </c>
@@ -2103,7 +2084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144">
       <c r="A144" t="s">
         <v>59</v>
       </c>
@@ -2111,7 +2092,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145">
       <c r="A145" t="s">
         <v>59</v>
       </c>
@@ -2119,7 +2100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146">
       <c r="A146" t="s">
         <v>60</v>
       </c>
@@ -2127,7 +2108,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="A147" t="s">
         <v>60</v>
       </c>
@@ -2135,7 +2116,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148">
       <c r="A148" t="s">
         <v>60</v>
       </c>
@@ -2143,7 +2124,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149">
       <c r="A149" t="s">
         <v>60</v>
       </c>
@@ -2151,7 +2132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150">
       <c r="A150" t="s">
         <v>61</v>
       </c>
@@ -2159,7 +2140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151">
       <c r="A151" t="s">
         <v>61</v>
       </c>
@@ -2167,7 +2148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152">
       <c r="A152" t="s">
         <v>61</v>
       </c>
@@ -2175,7 +2156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153">
       <c r="A153" t="s">
         <v>61</v>
       </c>
@@ -2183,7 +2164,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154">
       <c r="A154" t="s">
         <v>62</v>
       </c>
@@ -2191,7 +2172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155">
       <c r="A155" t="s">
         <v>62</v>
       </c>
@@ -2199,7 +2180,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156">
       <c r="A156" t="s">
         <v>62</v>
       </c>
@@ -2207,7 +2188,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157">
       <c r="A157" t="s">
         <v>62</v>
       </c>
@@ -2215,7 +2196,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158">
       <c r="A158" t="s">
         <v>63</v>
       </c>
@@ -2223,7 +2204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159">
       <c r="A159" t="s">
         <v>63</v>
       </c>
@@ -2231,7 +2212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160">
       <c r="A160" t="s">
         <v>63</v>
       </c>
@@ -2239,7 +2220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161">
       <c r="A161" t="s">
         <v>63</v>
       </c>
@@ -2247,7 +2228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162">
       <c r="A162" t="s">
         <v>64</v>
       </c>
@@ -2255,7 +2236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163">
       <c r="A163" t="s">
         <v>64</v>
       </c>
@@ -2263,7 +2244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164">
       <c r="A164" t="s">
         <v>64</v>
       </c>
@@ -2271,7 +2252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165">
       <c r="A165" t="s">
         <v>64</v>
       </c>
@@ -2279,7 +2260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166">
       <c r="A166" t="s">
         <v>65</v>
       </c>
@@ -2287,7 +2268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="A167" t="s">
         <v>65</v>
       </c>
@@ -2295,7 +2276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168">
       <c r="A168" t="s">
         <v>65</v>
       </c>
@@ -2303,7 +2284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169">
       <c r="A169" t="s">
         <v>65</v>
       </c>
@@ -2311,7 +2292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170">
       <c r="A170" t="s">
         <v>66</v>
       </c>
@@ -2319,7 +2300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171">
       <c r="A171" t="s">
         <v>66</v>
       </c>
@@ -2327,7 +2308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172">
       <c r="A172" t="s">
         <v>66</v>
       </c>
@@ -2335,7 +2316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173">
       <c r="A173" t="s">
         <v>66</v>
       </c>
@@ -2343,7 +2324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174">
       <c r="A174" t="s">
         <v>67</v>
       </c>
@@ -2351,7 +2332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175">
       <c r="A175" t="s">
         <v>67</v>
       </c>
@@ -2359,7 +2340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176">
       <c r="A176" t="s">
         <v>67</v>
       </c>
@@ -2367,7 +2348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177">
       <c r="A177" t="s">
         <v>67</v>
       </c>
@@ -2375,7 +2356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178">
       <c r="A178" t="s">
         <v>68</v>
       </c>
@@ -2383,7 +2364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179">
       <c r="A179" t="s">
         <v>68</v>
       </c>
@@ -2391,7 +2372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180">
       <c r="A180" t="s">
         <v>68</v>
       </c>
@@ -2399,7 +2380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181">
       <c r="A181" t="s">
         <v>68</v>
       </c>
@@ -2407,7 +2388,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182">
       <c r="A182" t="s">
         <v>69</v>
       </c>
@@ -2415,7 +2396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183">
       <c r="A183" t="s">
         <v>69</v>
       </c>
@@ -2423,7 +2404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184">
       <c r="A184" t="s">
         <v>69</v>
       </c>
@@ -2431,7 +2412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185">
       <c r="A185" t="s">
         <v>69</v>
       </c>
@@ -2439,7 +2420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186">
       <c r="A186" t="s">
         <v>70</v>
       </c>
@@ -2447,7 +2428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187">
       <c r="A187" t="s">
         <v>70</v>
       </c>
@@ -2455,7 +2436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188">
       <c r="A188" t="s">
         <v>70</v>
       </c>
@@ -2463,7 +2444,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189">
       <c r="A189" t="s">
         <v>70</v>
       </c>
@@ -2471,7 +2452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190">
       <c r="A190" t="s">
         <v>71</v>
       </c>
@@ -2479,7 +2460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191">
       <c r="A191" t="s">
         <v>71</v>
       </c>
@@ -2487,7 +2468,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192">
       <c r="A192" t="s">
         <v>71</v>
       </c>
@@ -2495,7 +2476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193">
       <c r="A193" t="s">
         <v>71</v>
       </c>
@@ -2503,7 +2484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194">
       <c r="A194" t="s">
         <v>72</v>
       </c>
@@ -2511,7 +2492,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195">
       <c r="A195" t="s">
         <v>72</v>
       </c>
@@ -2519,7 +2500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196">
       <c r="A196" t="s">
         <v>72</v>
       </c>
@@ -2527,7 +2508,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197">
       <c r="A197" t="s">
         <v>72</v>
       </c>
@@ -2535,7 +2516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198">
       <c r="A198" t="s">
         <v>73</v>
       </c>
@@ -2543,7 +2524,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199">
       <c r="A199" t="s">
         <v>73</v>
       </c>
@@ -2551,7 +2532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200">
       <c r="A200" t="s">
         <v>73</v>
       </c>
@@ -2559,7 +2540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201">
       <c r="A201" t="s">
         <v>73</v>
       </c>
@@ -2567,7 +2548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202">
       <c r="A202" t="s">
         <v>74</v>
       </c>
@@ -2575,7 +2556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203">
       <c r="A203" t="s">
         <v>74</v>
       </c>
@@ -2583,7 +2564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204">
       <c r="A204" t="s">
         <v>74</v>
       </c>
@@ -2591,7 +2572,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205">
       <c r="A205" t="s">
         <v>74</v>
       </c>
@@ -2599,7 +2580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206">
       <c r="A206" t="s">
         <v>75</v>
       </c>
@@ -2607,7 +2588,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207">
       <c r="A207" t="s">
         <v>75</v>
       </c>
@@ -2615,7 +2596,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208">
       <c r="A208" t="s">
         <v>75</v>
       </c>
@@ -2623,7 +2604,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209">
       <c r="A209" t="s">
         <v>75</v>
       </c>
@@ -2631,7 +2612,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210">
       <c r="A210" t="s">
         <v>76</v>
       </c>
@@ -2639,7 +2620,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211">
       <c r="A211" t="s">
         <v>76</v>
       </c>
@@ -2647,7 +2628,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212">
       <c r="A212" t="s">
         <v>76</v>
       </c>
@@ -2655,7 +2636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213">
       <c r="A213" t="s">
         <v>76</v>
       </c>
@@ -2663,7 +2644,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214">
       <c r="A214" t="s">
         <v>77</v>
       </c>
@@ -2671,7 +2652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215">
       <c r="A215" t="s">
         <v>77</v>
       </c>
@@ -2679,7 +2660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216">
       <c r="A216" t="s">
         <v>77</v>
       </c>
@@ -2687,7 +2668,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217">
       <c r="A217" t="s">
         <v>77</v>
       </c>
@@ -2695,7 +2676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218">
       <c r="A218" t="s">
         <v>78</v>
       </c>
@@ -2703,7 +2684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219">
       <c r="A219" t="s">
         <v>78</v>
       </c>
@@ -2711,7 +2692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220">
       <c r="A220" t="s">
         <v>78</v>
       </c>
@@ -2719,7 +2700,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221">
       <c r="A221" t="s">
         <v>78</v>
       </c>
@@ -2727,7 +2708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222">
       <c r="A222" t="s">
         <v>79</v>
       </c>
@@ -2735,7 +2716,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223">
       <c r="A223" t="s">
         <v>79</v>
       </c>
@@ -2743,7 +2724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -2751,7 +2732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225">
       <c r="A225" t="s">
         <v>79</v>
       </c>
@@ -2759,7 +2740,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226">
       <c r="A226" t="s">
         <v>80</v>
       </c>
@@ -2767,7 +2748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227">
       <c r="A227" t="s">
         <v>80</v>
       </c>
@@ -2775,7 +2756,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228">
       <c r="A228" t="s">
         <v>80</v>
       </c>
@@ -2783,7 +2764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229">
       <c r="A229" t="s">
         <v>80</v>
       </c>
@@ -2791,7 +2772,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230">
       <c r="A230" t="s">
         <v>81</v>
       </c>
@@ -2799,7 +2780,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231">
       <c r="A231" t="s">
         <v>81</v>
       </c>
@@ -2807,7 +2788,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232">
       <c r="A232" t="s">
         <v>81</v>
       </c>
@@ -2815,7 +2796,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233">
       <c r="A233" t="s">
         <v>81</v>
       </c>
@@ -2823,7 +2804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234">
       <c r="A234" t="s">
         <v>82</v>
       </c>
@@ -2831,7 +2812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="235">
       <c r="A235" t="s">
         <v>82</v>
       </c>
@@ -2839,7 +2820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236">
       <c r="A236" t="s">
         <v>82</v>
       </c>
@@ -2847,7 +2828,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237">
       <c r="A237" t="s">
         <v>82</v>
       </c>
@@ -2855,7 +2836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238">
       <c r="A238" t="s">
         <v>83</v>
       </c>
@@ -2863,7 +2844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="239">
       <c r="A239" t="s">
         <v>83</v>
       </c>
@@ -2871,7 +2852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240">
       <c r="A240" t="s">
         <v>83</v>
       </c>
@@ -2879,7 +2860,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241">
       <c r="A241" t="s">
         <v>83</v>
       </c>
@@ -2887,7 +2868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242">
       <c r="A242" t="s">
         <v>84</v>
       </c>
@@ -2895,7 +2876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243">
       <c r="A243" t="s">
         <v>84</v>
       </c>
@@ -2903,7 +2884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244">
       <c r="A244" t="s">
         <v>84</v>
       </c>
@@ -2911,7 +2892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245">
       <c r="A245" t="s">
         <v>84</v>
       </c>
@@ -2919,7 +2900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246">
       <c r="A246" t="s">
         <v>85</v>
       </c>
@@ -2927,7 +2908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247">
       <c r="A247" t="s">
         <v>85</v>
       </c>
@@ -2935,7 +2916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248">
       <c r="A248" t="s">
         <v>85</v>
       </c>
@@ -2943,7 +2924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249">
       <c r="A249" t="s">
         <v>85</v>
       </c>
@@ -2951,7 +2932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250">
       <c r="A250" t="s">
         <v>86</v>
       </c>
@@ -2959,7 +2940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251">
       <c r="A251" t="s">
         <v>86</v>
       </c>
@@ -2967,7 +2948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252">
       <c r="A252" t="s">
         <v>86</v>
       </c>
@@ -2975,7 +2956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253">
       <c r="A253" t="s">
         <v>86</v>
       </c>
@@ -2983,7 +2964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254">
       <c r="A254" t="s">
         <v>87</v>
       </c>
@@ -2991,7 +2972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255">
       <c r="A255" t="s">
         <v>87</v>
       </c>
@@ -2999,7 +2980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256">
       <c r="A256" t="s">
         <v>87</v>
       </c>
@@ -3007,7 +2988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="257">
       <c r="A257" t="s">
         <v>87</v>
       </c>
@@ -3015,7 +2996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="258">
       <c r="A258" t="s">
         <v>88</v>
       </c>
@@ -3023,7 +3004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="259">
       <c r="A259" t="s">
         <v>88</v>
       </c>
@@ -3031,7 +3012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="260">
       <c r="A260" t="s">
         <v>88</v>
       </c>
@@ -3039,7 +3020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="261">
       <c r="A261" t="s">
         <v>88</v>
       </c>
@@ -3047,7 +3028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="262">
       <c r="A262" t="s">
         <v>89</v>
       </c>
@@ -3055,7 +3036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="263">
       <c r="A263" t="s">
         <v>89</v>
       </c>
@@ -3063,7 +3044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="264">
       <c r="A264" t="s">
         <v>89</v>
       </c>
@@ -3071,7 +3052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="265">
       <c r="A265" t="s">
         <v>89</v>
       </c>
@@ -3079,7 +3060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="266">
       <c r="A266" t="s">
         <v>90</v>
       </c>
@@ -3087,7 +3068,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="267">
       <c r="A267" t="s">
         <v>90</v>
       </c>
@@ -3095,7 +3076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="268">
       <c r="A268" t="s">
         <v>90</v>
       </c>
@@ -3103,7 +3084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="269">
       <c r="A269" t="s">
         <v>90</v>
       </c>
@@ -3111,7 +3092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="270">
       <c r="A270" t="s">
         <v>91</v>
       </c>
@@ -3119,7 +3100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="271">
       <c r="A271" t="s">
         <v>91</v>
       </c>
@@ -3127,7 +3108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="272">
       <c r="A272" t="s">
         <v>91</v>
       </c>
@@ -3135,7 +3116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273">
       <c r="A273" t="s">
         <v>91</v>
       </c>
@@ -3143,7 +3124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274">
       <c r="A274" t="s">
         <v>92</v>
       </c>
@@ -3151,7 +3132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275">
       <c r="A275" t="s">
         <v>92</v>
       </c>
@@ -3159,7 +3140,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276">
       <c r="A276" t="s">
         <v>92</v>
       </c>
@@ -3167,7 +3148,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277">
       <c r="A277" t="s">
         <v>92</v>
       </c>
@@ -3175,7 +3156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278">
       <c r="A278" t="s">
         <v>93</v>
       </c>
@@ -3183,7 +3164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279">
       <c r="A279" t="s">
         <v>93</v>
       </c>
@@ -3191,7 +3172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280">
       <c r="A280" t="s">
         <v>93</v>
       </c>
@@ -3199,7 +3180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281">
       <c r="A281" t="s">
         <v>93</v>
       </c>
@@ -3207,7 +3188,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282">
       <c r="A282" t="s">
         <v>94</v>
       </c>
@@ -3215,7 +3196,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283">
       <c r="A283" t="s">
         <v>94</v>
       </c>
@@ -3223,7 +3204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284">
       <c r="A284" t="s">
         <v>94</v>
       </c>
@@ -3231,7 +3212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285">
       <c r="A285" t="s">
         <v>94</v>
       </c>
@@ -3239,7 +3220,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286">
       <c r="A286" t="s">
         <v>95</v>
       </c>
@@ -3247,7 +3228,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287">
       <c r="A287" t="s">
         <v>95</v>
       </c>
@@ -3255,7 +3236,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288">
       <c r="A288" t="s">
         <v>95</v>
       </c>
@@ -3263,7 +3244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289">
       <c r="A289" t="s">
         <v>95</v>
       </c>
@@ -3271,7 +3252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290">
       <c r="A290" t="s">
         <v>96</v>
       </c>
@@ -3279,7 +3260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291">
       <c r="A291" t="s">
         <v>96</v>
       </c>
@@ -3287,7 +3268,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292">
       <c r="A292" t="s">
         <v>96</v>
       </c>
@@ -3295,7 +3276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293">
       <c r="A293" t="s">
         <v>96</v>
       </c>
@@ -3303,7 +3284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294">
       <c r="A294" t="s">
         <v>97</v>
       </c>
@@ -3311,7 +3292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295">
       <c r="A295" t="s">
         <v>97</v>
       </c>
@@ -3319,7 +3300,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296">
       <c r="A296" t="s">
         <v>97</v>
       </c>
@@ -3327,7 +3308,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297">
       <c r="A297" t="s">
         <v>97</v>
       </c>
@@ -3335,7 +3316,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298">
       <c r="A298" t="s">
         <v>98</v>
       </c>
@@ -3343,7 +3324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299">
       <c r="A299" t="s">
         <v>98</v>
       </c>
@@ -3351,7 +3332,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300">
       <c r="A300" t="s">
         <v>98</v>
       </c>
@@ -3359,7 +3340,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301">
       <c r="A301" t="s">
         <v>98</v>
       </c>
@@ -3367,7 +3348,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302">
       <c r="A302" t="s">
         <v>99</v>
       </c>
@@ -3375,7 +3356,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303">
       <c r="A303" t="s">
         <v>99</v>
       </c>
@@ -3383,7 +3364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304">
       <c r="A304" t="s">
         <v>99</v>
       </c>
@@ -3391,7 +3372,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="305">
       <c r="A305" t="s">
         <v>99</v>
       </c>
@@ -3399,7 +3380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="306">
       <c r="A306" t="s">
         <v>100</v>
       </c>
@@ -3407,7 +3388,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="307">
       <c r="A307" t="s">
         <v>100</v>
       </c>
@@ -3415,7 +3396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="308">
       <c r="A308" t="s">
         <v>100</v>
       </c>
@@ -3423,7 +3404,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="309">
       <c r="A309" t="s">
         <v>100</v>
       </c>
@@ -3431,7 +3412,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="310">
       <c r="A310" t="s">
         <v>101</v>
       </c>
@@ -3439,7 +3420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="311">
       <c r="A311" t="s">
         <v>101</v>
       </c>
@@ -3447,7 +3428,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="312">
       <c r="A312" t="s">
         <v>101</v>
       </c>
@@ -3455,7 +3436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="313">
       <c r="A313" t="s">
         <v>101</v>
       </c>
@@ -3463,7 +3444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="314">
       <c r="A314" t="s">
         <v>102</v>
       </c>
@@ -3471,7 +3452,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="315">
       <c r="A315" t="s">
         <v>102</v>
       </c>
@@ -3479,7 +3460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="316">
       <c r="A316" t="s">
         <v>102</v>
       </c>
@@ -3487,7 +3468,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="317">
       <c r="A317" t="s">
         <v>102</v>
       </c>
@@ -3495,7 +3476,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="318">
       <c r="A318" t="s">
         <v>103</v>
       </c>
@@ -3503,7 +3484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="319">
       <c r="A319" t="s">
         <v>103</v>
       </c>
@@ -3511,7 +3492,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="320">
       <c r="A320" t="s">
         <v>103</v>
       </c>
@@ -3519,7 +3500,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321">
       <c r="A321" t="s">
         <v>103</v>
       </c>
@@ -3527,7 +3508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322">
       <c r="A322" t="s">
         <v>104</v>
       </c>
@@ -3535,7 +3516,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323">
       <c r="A323" t="s">
         <v>104</v>
       </c>
@@ -3543,7 +3524,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324">
       <c r="A324" t="s">
         <v>104</v>
       </c>
@@ -3551,7 +3532,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325">
       <c r="A325" t="s">
         <v>104</v>
       </c>
@@ -3559,7 +3540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326">
       <c r="A326" t="s">
         <v>105</v>
       </c>
@@ -3567,7 +3548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327">
       <c r="A327" t="s">
         <v>105</v>
       </c>
@@ -3575,7 +3556,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328">
       <c r="A328" t="s">
         <v>105</v>
       </c>
@@ -3583,7 +3564,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329">
       <c r="A329" t="s">
         <v>105</v>
       </c>
@@ -3591,7 +3572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330">
       <c r="A330" t="s">
         <v>106</v>
       </c>
@@ -3599,7 +3580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331">
       <c r="A331" t="s">
         <v>106</v>
       </c>
@@ -3607,7 +3588,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332">
       <c r="A332" t="s">
         <v>106</v>
       </c>
@@ -3615,7 +3596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333">
       <c r="A333" t="s">
         <v>106</v>
       </c>
@@ -3623,7 +3604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334">
       <c r="A334" t="s">
         <v>107</v>
       </c>
@@ -3631,7 +3612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335">
       <c r="A335" t="s">
         <v>107</v>
       </c>
@@ -3639,7 +3620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336">
       <c r="A336" t="s">
         <v>107</v>
       </c>
@@ -3647,7 +3628,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337">
       <c r="A337" t="s">
         <v>107</v>
       </c>
@@ -3655,7 +3636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338">
       <c r="A338" t="s">
         <v>108</v>
       </c>
@@ -3663,7 +3644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339">
       <c r="A339" t="s">
         <v>108</v>
       </c>
@@ -3671,7 +3652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340">
       <c r="A340" t="s">
         <v>108</v>
       </c>
@@ -3679,7 +3660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341">
       <c r="A341" t="s">
         <v>108</v>
       </c>
@@ -3687,7 +3668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342">
       <c r="A342" t="s">
         <v>109</v>
       </c>
@@ -3695,7 +3676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343">
       <c r="A343" t="s">
         <v>109</v>
       </c>
@@ -3703,7 +3684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344">
       <c r="A344" t="s">
         <v>109</v>
       </c>
@@ -3711,7 +3692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345">
       <c r="A345" t="s">
         <v>109</v>
       </c>
@@ -3719,7 +3700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346">
       <c r="A346" t="s">
         <v>110</v>
       </c>
@@ -3727,7 +3708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347">
       <c r="A347" t="s">
         <v>110</v>
       </c>
@@ -3735,7 +3716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="348">
       <c r="A348" t="s">
         <v>110</v>
       </c>
@@ -3743,7 +3724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="349">
       <c r="A349" t="s">
         <v>110</v>
       </c>
@@ -3751,7 +3732,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="350">
       <c r="A350" t="s">
         <v>111</v>
       </c>
@@ -3759,7 +3740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="351">
       <c r="A351" t="s">
         <v>111</v>
       </c>
@@ -3767,7 +3748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="352">
       <c r="A352" t="s">
         <v>111</v>
       </c>
@@ -3775,7 +3756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="353">
       <c r="A353" t="s">
         <v>111</v>
       </c>
@@ -3783,7 +3764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="354">
       <c r="A354" t="s">
         <v>112</v>
       </c>
@@ -3791,7 +3772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="355">
       <c r="A355" t="s">
         <v>112</v>
       </c>
@@ -3799,7 +3780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="356">
       <c r="A356" t="s">
         <v>112</v>
       </c>
@@ -3807,7 +3788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="357">
       <c r="A357" t="s">
         <v>112</v>
       </c>
@@ -3815,7 +3796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="358">
       <c r="A358" t="s">
         <v>113</v>
       </c>
@@ -3823,7 +3804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="359">
       <c r="A359" t="s">
         <v>113</v>
       </c>
@@ -3831,7 +3812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="360">
       <c r="A360" t="s">
         <v>113</v>
       </c>
@@ -3839,7 +3820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="361">
       <c r="A361" t="s">
         <v>113</v>
       </c>
@@ -3847,7 +3828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="362">
       <c r="A362" t="s">
         <v>114</v>
       </c>
@@ -3855,7 +3836,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="363">
       <c r="A363" t="s">
         <v>114</v>
       </c>
@@ -3863,7 +3844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="364">
       <c r="A364" t="s">
         <v>114</v>
       </c>
@@ -3871,7 +3852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="365">
       <c r="A365" t="s">
         <v>114</v>
       </c>
@@ -3879,7 +3860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="366">
       <c r="A366" t="s">
         <v>115</v>
       </c>
@@ -3887,7 +3868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="367">
       <c r="A367" t="s">
         <v>115</v>
       </c>
@@ -3895,7 +3876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="368">
       <c r="A368" t="s">
         <v>115</v>
       </c>
@@ -3903,7 +3884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="369">
       <c r="A369" t="s">
         <v>115</v>
       </c>
@@ -3911,7 +3892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="370">
       <c r="A370" t="s">
         <v>116</v>
       </c>
@@ -3919,7 +3900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="371">
       <c r="A371" t="s">
         <v>116</v>
       </c>
@@ -3927,7 +3908,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="372">
       <c r="A372" t="s">
         <v>116</v>
       </c>
@@ -3935,7 +3916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="373">
       <c r="A373" t="s">
         <v>116</v>
       </c>
@@ -3943,7 +3924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="374">
       <c r="A374" t="s">
         <v>117</v>
       </c>
@@ -3951,7 +3932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="375">
       <c r="A375" t="s">
         <v>117</v>
       </c>
@@ -3959,7 +3940,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="376">
       <c r="A376" t="s">
         <v>117</v>
       </c>
@@ -3967,7 +3948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="377">
       <c r="A377" t="s">
         <v>117</v>
       </c>
@@ -3975,7 +3956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="378">
       <c r="A378" t="s">
         <v>118</v>
       </c>
@@ -3983,7 +3964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="379">
       <c r="A379" t="s">
         <v>118</v>
       </c>
@@ -3991,7 +3972,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="380">
       <c r="A380" t="s">
         <v>118</v>
       </c>
@@ -3999,7 +3980,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="381">
       <c r="A381" t="s">
         <v>118</v>
       </c>
@@ -4007,7 +3988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="382">
       <c r="A382" t="s">
         <v>119</v>
       </c>
@@ -4015,7 +3996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="383">
       <c r="A383" t="s">
         <v>119</v>
       </c>
@@ -4023,7 +4004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="384">
       <c r="A384" t="s">
         <v>119</v>
       </c>
@@ -4031,7 +4012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="385">
       <c r="A385" t="s">
         <v>119</v>
       </c>
@@ -4039,7 +4020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="386">
       <c r="A386" t="s">
         <v>120</v>
       </c>
@@ -4047,7 +4028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="387">
       <c r="A387" t="s">
         <v>120</v>
       </c>
@@ -4055,7 +4036,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="388">
       <c r="A388" t="s">
         <v>120</v>
       </c>
@@ -4063,7 +4044,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="389">
       <c r="A389" t="s">
         <v>120</v>
       </c>
@@ -4071,7 +4052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="390">
       <c r="A390" t="s">
         <v>121</v>
       </c>
@@ -4079,7 +4060,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="391">
       <c r="A391" t="s">
         <v>121</v>
       </c>
@@ -4087,7 +4068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="392">
       <c r="A392" t="s">
         <v>121</v>
       </c>
@@ -4095,7 +4076,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="393">
       <c r="A393" t="s">
         <v>121</v>
       </c>
@@ -4103,7 +4084,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="394">
       <c r="A394" t="s">
         <v>122</v>
       </c>
@@ -4111,7 +4092,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="395">
       <c r="A395" t="s">
         <v>122</v>
       </c>
@@ -4119,7 +4100,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="396">
       <c r="A396" t="s">
         <v>122</v>
       </c>
@@ -4127,7 +4108,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="397">
       <c r="A397" t="s">
         <v>122</v>
       </c>
@@ -4135,7 +4116,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="398">
       <c r="A398" t="s">
         <v>123</v>
       </c>
@@ -4143,7 +4124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="399">
       <c r="A399" t="s">
         <v>123</v>
       </c>
@@ -4151,7 +4132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="400">
       <c r="A400" t="s">
         <v>123</v>
       </c>
@@ -4159,7 +4140,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="401">
       <c r="A401" t="s">
         <v>123</v>
       </c>
@@ -4167,7 +4148,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="402">
       <c r="A402" t="s">
         <v>124</v>
       </c>
@@ -4175,7 +4156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="403">
       <c r="A403" t="s">
         <v>124</v>
       </c>
@@ -4183,7 +4164,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="404">
       <c r="A404" t="s">
         <v>124</v>
       </c>
@@ -4191,7 +4172,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="405">
       <c r="A405" t="s">
         <v>124</v>
       </c>
@@ -4199,7 +4180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="406">
       <c r="A406" t="s">
         <v>125</v>
       </c>
@@ -4207,7 +4188,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="407">
       <c r="A407" t="s">
         <v>125</v>
       </c>
@@ -4215,7 +4196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="408">
       <c r="A408" t="s">
         <v>125</v>
       </c>
@@ -4223,7 +4204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="409">
       <c r="A409" t="s">
         <v>125</v>
       </c>
@@ -4231,7 +4212,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="410">
       <c r="A410" t="s">
         <v>126</v>
       </c>
@@ -4239,7 +4220,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="411">
       <c r="A411" t="s">
         <v>126</v>
       </c>
@@ -4247,7 +4228,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="412">
       <c r="A412" t="s">
         <v>126</v>
       </c>
@@ -4255,7 +4236,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="413">
       <c r="A413" t="s">
         <v>126</v>
       </c>
@@ -4263,7 +4244,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="414">
       <c r="A414" t="s">
         <v>127</v>
       </c>
@@ -4271,7 +4252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="415">
       <c r="A415" t="s">
         <v>127</v>
       </c>
@@ -4279,7 +4260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="416">
       <c r="A416" t="s">
         <v>127</v>
       </c>
@@ -4287,7 +4268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="417">
       <c r="A417" t="s">
         <v>127</v>
       </c>
@@ -4295,7 +4276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="418">
       <c r="A418" t="s">
         <v>128</v>
       </c>
@@ -4303,7 +4284,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="419">
       <c r="A419" t="s">
         <v>128</v>
       </c>
@@ -4311,7 +4292,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="420">
       <c r="A420" t="s">
         <v>128</v>
       </c>
@@ -4319,7 +4300,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="421">
       <c r="A421" t="s">
         <v>128</v>
       </c>
@@ -4327,7 +4308,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="422">
       <c r="A422" t="s">
         <v>129</v>
       </c>
@@ -4335,7 +4316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="423">
       <c r="A423" t="s">
         <v>129</v>
       </c>
@@ -4343,7 +4324,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="424">
       <c r="A424" t="s">
         <v>129</v>
       </c>
@@ -4351,7 +4332,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="425">
       <c r="A425" t="s">
         <v>129</v>
       </c>
@@ -4359,7 +4340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="426">
       <c r="A426" t="s">
         <v>130</v>
       </c>
@@ -4367,7 +4348,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="427">
       <c r="A427" t="s">
         <v>130</v>
       </c>
@@ -4375,7 +4356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="428">
       <c r="A428" t="s">
         <v>130</v>
       </c>
@@ -4383,7 +4364,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="429">
       <c r="A429" t="s">
         <v>130</v>
       </c>
@@ -4391,7 +4372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="430">
       <c r="A430" t="s">
         <v>131</v>
       </c>
@@ -4399,7 +4380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="431">
       <c r="A431" t="s">
         <v>131</v>
       </c>
@@ -4407,7 +4388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="432">
       <c r="A432" t="s">
         <v>131</v>
       </c>
@@ -4415,7 +4396,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="433">
       <c r="A433" t="s">
         <v>131</v>
       </c>
@@ -4423,7 +4404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="434">
       <c r="A434" t="s">
         <v>132</v>
       </c>
@@ -4431,7 +4412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="435">
       <c r="A435" t="s">
         <v>132</v>
       </c>
@@ -4439,7 +4420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="436">
       <c r="A436" t="s">
         <v>132</v>
       </c>
@@ -4447,7 +4428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="437">
       <c r="A437" t="s">
         <v>132</v>
       </c>
@@ -4455,7 +4436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438">
       <c r="A438" t="s">
         <v>133</v>
       </c>
@@ -4463,7 +4444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="439">
       <c r="A439" t="s">
         <v>133</v>
       </c>
@@ -4471,7 +4452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="440">
       <c r="A440" t="s">
         <v>133</v>
       </c>
@@ -4479,7 +4460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="441">
       <c r="A441" t="s">
         <v>133</v>
       </c>
@@ -4487,7 +4468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="442">
       <c r="A442" t="s">
         <v>134</v>
       </c>
@@ -4495,7 +4476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="443">
       <c r="A443" t="s">
         <v>134</v>
       </c>
@@ -4503,7 +4484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="444">
       <c r="A444" t="s">
         <v>134</v>
       </c>
@@ -4511,7 +4492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="445">
       <c r="A445" t="s">
         <v>134</v>
       </c>
@@ -4519,7 +4500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="446">
       <c r="A446" t="s">
         <v>135</v>
       </c>
@@ -4527,7 +4508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="447">
       <c r="A447" t="s">
         <v>135</v>
       </c>
@@ -4535,7 +4516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="448">
       <c r="A448" t="s">
         <v>135</v>
       </c>
@@ -4543,7 +4524,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="449">
       <c r="A449" t="s">
         <v>135</v>
       </c>
@@ -4551,7 +4532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="450">
       <c r="A450" t="s">
         <v>136</v>
       </c>
@@ -4559,7 +4540,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="451">
       <c r="A451" t="s">
         <v>136</v>
       </c>
@@ -4567,7 +4548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="452">
       <c r="A452" t="s">
         <v>136</v>
       </c>
@@ -4575,7 +4556,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="453">
       <c r="A453" t="s">
         <v>136</v>
       </c>
@@ -4583,7 +4564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="454">
       <c r="A454" t="s">
         <v>137</v>
       </c>
@@ -4591,7 +4572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="455">
       <c r="A455" t="s">
         <v>137</v>
       </c>
@@ -4599,7 +4580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="456">
       <c r="A456" t="s">
         <v>137</v>
       </c>
@@ -4607,7 +4588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="457">
       <c r="A457" t="s">
         <v>137</v>
       </c>
@@ -4615,7 +4596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="458">
       <c r="A458" t="s">
         <v>138</v>
       </c>
@@ -4623,7 +4604,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="459">
       <c r="A459" t="s">
         <v>138</v>
       </c>
@@ -4631,7 +4612,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="460">
       <c r="A460" t="s">
         <v>138</v>
       </c>
@@ -4639,7 +4620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="461">
       <c r="A461" t="s">
         <v>138</v>
       </c>
@@ -4647,7 +4628,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="462">
       <c r="A462" t="s">
         <v>139</v>
       </c>
@@ -4655,7 +4636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="463">
       <c r="A463" t="s">
         <v>139</v>
       </c>
@@ -4663,7 +4644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="464">
       <c r="A464" t="s">
         <v>139</v>
       </c>
@@ -4671,7 +4652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="465">
       <c r="A465" t="s">
         <v>139</v>
       </c>
@@ -4679,7 +4660,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="466">
       <c r="A466" t="s">
         <v>140</v>
       </c>
@@ -4687,7 +4668,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="467">
       <c r="A467" t="s">
         <v>140</v>
       </c>
@@ -4695,7 +4676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="468">
       <c r="A468" t="s">
         <v>140</v>
       </c>
@@ -4703,7 +4684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="469">
       <c r="A469" t="s">
         <v>140</v>
       </c>
@@ -4711,7 +4692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="470">
       <c r="A470" t="s">
         <v>141</v>
       </c>
@@ -4719,7 +4700,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="471">
       <c r="A471" t="s">
         <v>141</v>
       </c>
@@ -4727,7 +4708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="472">
       <c r="A472" t="s">
         <v>141</v>
       </c>
@@ -4735,7 +4716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="473">
       <c r="A473" t="s">
         <v>141</v>
       </c>
@@ -4743,7 +4724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="474">
       <c r="A474" t="s">
         <v>142</v>
       </c>
@@ -4751,7 +4732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="475">
       <c r="A475" t="s">
         <v>142</v>
       </c>
@@ -4759,7 +4740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="476">
       <c r="A476" t="s">
         <v>142</v>
       </c>
@@ -4767,7 +4748,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="477">
       <c r="A477" t="s">
         <v>142</v>
       </c>
@@ -4775,7 +4756,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="478">
       <c r="A478" t="s">
         <v>143</v>
       </c>
@@ -4783,7 +4764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="479">
       <c r="A479" t="s">
         <v>143</v>
       </c>
@@ -4791,7 +4772,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="480">
       <c r="A480" t="s">
         <v>143</v>
       </c>
@@ -4799,7 +4780,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="481">
       <c r="A481" t="s">
         <v>143</v>
       </c>
@@ -4807,7 +4788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="482">
       <c r="A482" t="s">
         <v>144</v>
       </c>
@@ -4815,7 +4796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="483">
       <c r="A483" t="s">
         <v>144</v>
       </c>
@@ -4823,7 +4804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="484">
       <c r="A484" t="s">
         <v>144</v>
       </c>
@@ -4831,7 +4812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="485">
       <c r="A485" t="s">
         <v>144</v>
       </c>
@@ -4839,7 +4820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="486">
       <c r="A486" t="s">
         <v>145</v>
       </c>
@@ -4847,7 +4828,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="487">
       <c r="A487" t="s">
         <v>145</v>
       </c>
@@ -4855,7 +4836,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="488">
       <c r="A488" t="s">
         <v>145</v>
       </c>
@@ -4863,7 +4844,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="489">
       <c r="A489" t="s">
         <v>145</v>
       </c>
@@ -4871,7 +4852,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="490">
       <c r="A490" t="s">
         <v>146</v>
       </c>
@@ -4879,7 +4860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="491">
       <c r="A491" t="s">
         <v>146</v>
       </c>
@@ -4887,7 +4868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="492">
       <c r="A492" t="s">
         <v>146</v>
       </c>
@@ -4895,7 +4876,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="493">
       <c r="A493" t="s">
         <v>146</v>
       </c>
@@ -4903,7 +4884,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="494">
       <c r="A494" t="s">
         <v>147</v>
       </c>
@@ -4911,7 +4892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="495">
       <c r="A495" t="s">
         <v>147</v>
       </c>
@@ -4919,7 +4900,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="496">
       <c r="A496" t="s">
         <v>147</v>
       </c>
@@ -4927,7 +4908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="497">
       <c r="A497" t="s">
         <v>147</v>
       </c>
@@ -4935,7 +4916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="498">
       <c r="A498" t="s">
         <v>148</v>
       </c>
@@ -4943,7 +4924,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="499">
       <c r="A499" t="s">
         <v>148</v>
       </c>
@@ -4951,7 +4932,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="500">
       <c r="A500" t="s">
         <v>148</v>
       </c>
@@ -4959,7 +4940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="501">
       <c r="A501" t="s">
         <v>148</v>
       </c>
@@ -4967,7 +4948,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="502">
       <c r="A502" t="s">
         <v>149</v>
       </c>
@@ -4975,7 +4956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="503">
       <c r="A503" t="s">
         <v>149</v>
       </c>
@@ -4983,7 +4964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="504">
       <c r="A504" t="s">
         <v>149</v>
       </c>
@@ -4991,7 +4972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="505">
       <c r="A505" t="s">
         <v>149</v>
       </c>
@@ -4999,7 +4980,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="506">
       <c r="A506" t="s">
         <v>150</v>
       </c>
@@ -5007,7 +4988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="507">
       <c r="A507" t="s">
         <v>150</v>
       </c>
@@ -5015,7 +4996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="508">
       <c r="A508" t="s">
         <v>150</v>
       </c>
@@ -5023,7 +5004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="509">
       <c r="A509" t="s">
         <v>150</v>
       </c>
@@ -5031,7 +5012,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="510">
       <c r="A510" t="s">
         <v>151</v>
       </c>
@@ -5039,7 +5020,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="511">
       <c r="A511" t="s">
         <v>151</v>
       </c>
@@ -5047,7 +5028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="512">
       <c r="A512" t="s">
         <v>151</v>
       </c>
@@ -5055,7 +5036,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="513">
       <c r="A513" t="s">
         <v>151</v>
       </c>
@@ -5063,7 +5044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="514">
       <c r="A514" t="s">
         <v>152</v>
       </c>
@@ -5071,7 +5052,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="515">
       <c r="A515" t="s">
         <v>152</v>
       </c>
@@ -5079,7 +5060,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="516">
       <c r="A516" t="s">
         <v>152</v>
       </c>
@@ -5087,7 +5068,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="517">
       <c r="A517" t="s">
         <v>152</v>
       </c>
@@ -5095,7 +5076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="518">
       <c r="A518" t="s">
         <v>153</v>
       </c>
@@ -5103,7 +5084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="519">
       <c r="A519" t="s">
         <v>153</v>
       </c>
@@ -5111,7 +5092,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="520">
       <c r="A520" t="s">
         <v>153</v>
       </c>
@@ -5119,7 +5100,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="521">
       <c r="A521" t="s">
         <v>153</v>
       </c>
@@ -5127,7 +5108,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="522">
       <c r="A522" t="s">
         <v>154</v>
       </c>
@@ -5135,7 +5116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="523">
       <c r="A523" t="s">
         <v>154</v>
       </c>
@@ -5143,7 +5124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="524">
       <c r="A524" t="s">
         <v>154</v>
       </c>
@@ -5151,7 +5132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="525">
       <c r="A525" t="s">
         <v>154</v>
       </c>
@@ -5159,7 +5140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="526">
       <c r="A526" t="s">
         <v>155</v>
       </c>
@@ -5167,7 +5148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="527">
       <c r="A527" t="s">
         <v>155</v>
       </c>
@@ -5175,7 +5156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="528">
       <c r="A528" t="s">
         <v>155</v>
       </c>
@@ -5183,7 +5164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="529">
       <c r="A529" t="s">
         <v>155</v>
       </c>
@@ -5191,7 +5172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="530">
       <c r="A530" t="s">
         <v>156</v>
       </c>
@@ -5199,7 +5180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="531">
       <c r="A531" t="s">
         <v>156</v>
       </c>
@@ -5207,7 +5188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="532">
       <c r="A532" t="s">
         <v>156</v>
       </c>
@@ -5215,7 +5196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="533">
       <c r="A533" t="s">
         <v>156</v>
       </c>
@@ -5223,7 +5204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="534">
       <c r="A534" t="s">
         <v>157</v>
       </c>
@@ -5231,7 +5212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="535">
       <c r="A535" t="s">
         <v>157</v>
       </c>
@@ -5239,7 +5220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="536">
       <c r="A536" t="s">
         <v>157</v>
       </c>
@@ -5247,7 +5228,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="537">
       <c r="A537" t="s">
         <v>157</v>
       </c>
@@ -5255,7 +5236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="538">
       <c r="A538" t="s">
         <v>158</v>
       </c>
@@ -5263,7 +5244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="539">
       <c r="A539" t="s">
         <v>158</v>
       </c>
@@ -5271,7 +5252,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="540">
       <c r="A540" t="s">
         <v>158</v>
       </c>
@@ -5279,7 +5260,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="541">
       <c r="A541" t="s">
         <v>158</v>
       </c>
@@ -5287,7 +5268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="542">
       <c r="A542" t="s">
         <v>159</v>
       </c>
@@ -5295,7 +5276,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="543">
       <c r="A543" t="s">
         <v>159</v>
       </c>
@@ -5303,7 +5284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="544">
       <c r="A544" t="s">
         <v>159</v>
       </c>
@@ -5311,7 +5292,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="545">
       <c r="A545" t="s">
         <v>159</v>
       </c>
@@ -5319,7 +5300,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="546">
       <c r="A546" t="s">
         <v>160</v>
       </c>
@@ -5327,7 +5308,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="547">
       <c r="A547" t="s">
         <v>160</v>
       </c>
@@ -5335,7 +5316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="548">
       <c r="A548" t="s">
         <v>160</v>
       </c>
@@ -5343,7 +5324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="549">
       <c r="A549" t="s">
         <v>160</v>
       </c>
@@ -5351,7 +5332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="550">
       <c r="A550" t="s">
         <v>161</v>
       </c>
@@ -5359,7 +5340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="551">
       <c r="A551" t="s">
         <v>161</v>
       </c>
@@ -5367,7 +5348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="552">
       <c r="A552" t="s">
         <v>161</v>
       </c>
@@ -5375,7 +5356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="553">
       <c r="A553" t="s">
         <v>161</v>
       </c>
@@ -5383,7 +5364,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="554">
       <c r="A554" t="s">
         <v>162</v>
       </c>
@@ -5391,7 +5372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="555">
       <c r="A555" t="s">
         <v>162</v>
       </c>
@@ -5399,7 +5380,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="556">
       <c r="A556" t="s">
         <v>162</v>
       </c>
@@ -5407,7 +5388,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="557">
       <c r="A557" t="s">
         <v>162</v>
       </c>
@@ -5415,7 +5396,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="558">
       <c r="A558" t="s">
         <v>163</v>
       </c>
@@ -5423,7 +5404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="559">
       <c r="A559" t="s">
         <v>163</v>
       </c>
@@ -5431,7 +5412,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="560">
       <c r="A560" t="s">
         <v>163</v>
       </c>
@@ -5439,7 +5420,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="561">
       <c r="A561" t="s">
         <v>163</v>
       </c>
@@ -5447,7 +5428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="562">
       <c r="A562" t="s">
         <v>164</v>
       </c>
@@ -5455,7 +5436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="563">
       <c r="A563" t="s">
         <v>164</v>
       </c>
@@ -5463,7 +5444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="564">
       <c r="A564" t="s">
         <v>164</v>
       </c>
@@ -5471,7 +5452,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="565">
       <c r="A565" t="s">
         <v>164</v>
       </c>
@@ -5479,7 +5460,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="566">
       <c r="A566" t="s">
         <v>165</v>
       </c>
@@ -5487,7 +5468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="567">
       <c r="A567" t="s">
         <v>165</v>
       </c>
@@ -5495,7 +5476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="568">
       <c r="A568" t="s">
         <v>165</v>
       </c>
@@ -5503,7 +5484,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="569">
       <c r="A569" t="s">
         <v>165</v>
       </c>
@@ -5511,7 +5492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="570">
       <c r="A570" t="s">
         <v>166</v>
       </c>
@@ -5519,7 +5500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="571">
       <c r="A571" t="s">
         <v>166</v>
       </c>
@@ -5527,7 +5508,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="572">
       <c r="A572" t="s">
         <v>166</v>
       </c>
@@ -5535,7 +5516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="573">
       <c r="A573" t="s">
         <v>166</v>
       </c>
@@ -5543,7 +5524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="574">
       <c r="A574" t="s">
         <v>167</v>
       </c>
@@ -5551,7 +5532,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="575">
       <c r="A575" t="s">
         <v>167</v>
       </c>
@@ -5559,7 +5540,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="576">
       <c r="A576" t="s">
         <v>167</v>
       </c>
@@ -5567,7 +5548,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="577">
       <c r="A577" t="s">
         <v>167</v>
       </c>
@@ -5575,7 +5556,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="578">
       <c r="A578" t="s">
         <v>168</v>
       </c>
@@ -5583,7 +5564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="579">
       <c r="A579" t="s">
         <v>168</v>
       </c>
@@ -5591,7 +5572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="580">
       <c r="A580" t="s">
         <v>168</v>
       </c>
@@ -5599,7 +5580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="581">
       <c r="A581" t="s">
         <v>168</v>
       </c>
@@ -5607,7 +5588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="582">
       <c r="A582" t="s">
         <v>169</v>
       </c>
@@ -5615,7 +5596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="583">
       <c r="A583" t="s">
         <v>169</v>
       </c>
@@ -5623,7 +5604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="584">
       <c r="A584" t="s">
         <v>169</v>
       </c>
@@ -5631,7 +5612,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="585">
       <c r="A585" t="s">
         <v>169</v>
       </c>
@@ -5639,7 +5620,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="586">
       <c r="A586" t="s">
         <v>170</v>
       </c>
@@ -5647,7 +5628,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="587">
       <c r="A587" t="s">
         <v>170</v>
       </c>
@@ -5655,7 +5636,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="588">
       <c r="A588" t="s">
         <v>170</v>
       </c>
@@ -5663,7 +5644,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="589">
       <c r="A589" t="s">
         <v>170</v>
       </c>
@@ -5671,7 +5652,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="590">
       <c r="A590" t="s">
         <v>171</v>
       </c>
@@ -5679,7 +5660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="591">
       <c r="A591" t="s">
         <v>171</v>
       </c>
@@ -5687,7 +5668,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="592">
       <c r="A592" t="s">
         <v>171</v>
       </c>
@@ -5695,7 +5676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="593">
       <c r="A593" t="s">
         <v>171</v>
       </c>
@@ -5703,7 +5684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="594">
       <c r="A594" t="s">
         <v>172</v>
       </c>
@@ -5711,7 +5692,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="595">
       <c r="A595" t="s">
         <v>172</v>
       </c>
@@ -5719,7 +5700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="596">
       <c r="A596" t="s">
         <v>172</v>
       </c>
@@ -5727,7 +5708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="597">
       <c r="A597" t="s">
         <v>172</v>
       </c>
@@ -5735,7 +5716,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="598">
       <c r="A598" t="s">
         <v>173</v>
       </c>
@@ -5743,7 +5724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="599">
       <c r="A599" t="s">
         <v>173</v>
       </c>
@@ -5751,7 +5732,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="600">
       <c r="A600" t="s">
         <v>173</v>
       </c>
@@ -5759,7 +5740,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="601">
       <c r="A601" t="s">
         <v>173</v>
       </c>
@@ -5767,7 +5748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="602">
       <c r="A602" t="s">
         <v>174</v>
       </c>
@@ -5775,7 +5756,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="603">
       <c r="A603" t="s">
         <v>174</v>
       </c>
@@ -5783,7 +5764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="604">
       <c r="A604" t="s">
         <v>174</v>
       </c>
@@ -5791,7 +5772,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="605">
       <c r="A605" t="s">
         <v>174</v>
       </c>
@@ -5799,7 +5780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="606">
       <c r="A606" t="s">
         <v>175</v>
       </c>
@@ -5807,7 +5788,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="607">
       <c r="A607" t="s">
         <v>175</v>
       </c>
@@ -5815,7 +5796,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="608">
       <c r="A608" t="s">
         <v>175</v>
       </c>
@@ -5823,7 +5804,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="609">
       <c r="A609" t="s">
         <v>175</v>
       </c>
@@ -5831,7 +5812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="610">
       <c r="A610" t="s">
         <v>176</v>
       </c>
@@ -5839,7 +5820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="611">
       <c r="A611" t="s">
         <v>176</v>
       </c>
@@ -5847,7 +5828,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="612">
       <c r="A612" t="s">
         <v>176</v>
       </c>
@@ -5855,7 +5836,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="613">
       <c r="A613" t="s">
         <v>176</v>
       </c>
@@ -5863,7 +5844,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="614">
       <c r="A614" t="s">
         <v>177</v>
       </c>
@@ -5871,7 +5852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="615">
       <c r="A615" t="s">
         <v>177</v>
       </c>
@@ -5879,7 +5860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="616">
       <c r="A616" t="s">
         <v>177</v>
       </c>
@@ -5887,7 +5868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="617">
       <c r="A617" t="s">
         <v>177</v>
       </c>
@@ -5895,7 +5876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="618">
       <c r="A618" t="s">
         <v>178</v>
       </c>
@@ -5903,7 +5884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="619">
       <c r="A619" t="s">
         <v>178</v>
       </c>
@@ -5911,7 +5892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="620">
       <c r="A620" t="s">
         <v>178</v>
       </c>
@@ -5919,7 +5900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="621">
       <c r="A621" t="s">
         <v>178</v>
       </c>
@@ -5927,7 +5908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="622">
       <c r="A622" t="s">
         <v>179</v>
       </c>
@@ -5935,7 +5916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="623">
       <c r="A623" t="s">
         <v>179</v>
       </c>
@@ -5943,7 +5924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="624">
       <c r="A624" t="s">
         <v>179</v>
       </c>
@@ -5951,7 +5932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="625">
       <c r="A625" t="s">
         <v>179</v>
       </c>
@@ -5959,7 +5940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="626">
       <c r="A626" t="s">
         <v>180</v>
       </c>
@@ -5967,7 +5948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="627">
       <c r="A627" t="s">
         <v>180</v>
       </c>
@@ -5975,7 +5956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="628">
       <c r="A628" t="s">
         <v>180</v>
       </c>
@@ -5983,7 +5964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="629">
       <c r="A629" t="s">
         <v>180</v>
       </c>
@@ -5991,7 +5972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="630">
       <c r="A630" t="s">
         <v>181</v>
       </c>
@@ -5999,7 +5980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="631">
       <c r="A631" t="s">
         <v>181</v>
       </c>
@@ -6007,7 +5988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="632">
       <c r="A632" t="s">
         <v>181</v>
       </c>
@@ -6015,7 +5996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="633">
       <c r="A633" t="s">
         <v>181</v>
       </c>
@@ -6023,7 +6004,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="634">
       <c r="A634" t="s">
         <v>182</v>
       </c>
@@ -6031,7 +6012,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="635">
       <c r="A635" t="s">
         <v>182</v>
       </c>
@@ -6039,7 +6020,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="636">
       <c r="A636" t="s">
         <v>182</v>
       </c>
@@ -6047,7 +6028,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="637">
       <c r="A637" t="s">
         <v>182</v>
       </c>
@@ -6055,7 +6036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="638">
       <c r="A638" t="s">
         <v>183</v>
       </c>
@@ -6063,7 +6044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="639">
       <c r="A639" t="s">
         <v>183</v>
       </c>
@@ -6071,7 +6052,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="640">
       <c r="A640" t="s">
         <v>183</v>
       </c>
@@ -6079,7 +6060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="641">
       <c r="A641" t="s">
         <v>183</v>
       </c>
@@ -6087,7 +6068,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="642">
       <c r="A642" t="s">
         <v>184</v>
       </c>
@@ -6095,7 +6076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="643">
       <c r="A643" t="s">
         <v>184</v>
       </c>
@@ -6103,7 +6084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="644">
       <c r="A644" t="s">
         <v>184</v>
       </c>
@@ -6111,7 +6092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="645">
       <c r="A645" t="s">
         <v>184</v>
       </c>
@@ -6119,7 +6100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="646">
       <c r="A646" t="s">
         <v>185</v>
       </c>
@@ -6127,7 +6108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="647">
       <c r="A647" t="s">
         <v>185</v>
       </c>
@@ -6135,7 +6116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="648">
       <c r="A648" t="s">
         <v>185</v>
       </c>
@@ -6143,7 +6124,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="649">
       <c r="A649" t="s">
         <v>185</v>
       </c>
@@ -6151,7 +6132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="650">
       <c r="A650" t="s">
         <v>186</v>
       </c>
@@ -6159,7 +6140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="651">
       <c r="A651" t="s">
         <v>186</v>
       </c>
@@ -6167,7 +6148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="652">
       <c r="A652" t="s">
         <v>186</v>
       </c>
@@ -6175,7 +6156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="653">
       <c r="A653" t="s">
         <v>186</v>
       </c>
@@ -6183,7 +6164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="654">
       <c r="A654" t="s">
         <v>187</v>
       </c>
@@ -6191,7 +6172,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="655">
       <c r="A655" t="s">
         <v>187</v>
       </c>
@@ -6199,7 +6180,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="656">
       <c r="A656" t="s">
         <v>187</v>
       </c>
@@ -6207,7 +6188,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="657">
       <c r="A657" t="s">
         <v>187</v>
       </c>
@@ -6215,7 +6196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="658">
       <c r="A658" t="s">
         <v>188</v>
       </c>
@@ -6223,7 +6204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="659">
       <c r="A659" t="s">
         <v>188</v>
       </c>
@@ -6231,7 +6212,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="660">
       <c r="A660" t="s">
         <v>188</v>
       </c>
@@ -6239,7 +6220,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="661">
       <c r="A661" t="s">
         <v>188</v>
       </c>
@@ -6247,7 +6228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="662">
       <c r="A662" t="s">
         <v>189</v>
       </c>
@@ -6255,7 +6236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="663">
       <c r="A663" t="s">
         <v>189</v>
       </c>
@@ -6263,7 +6244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="664">
       <c r="A664" t="s">
         <v>189</v>
       </c>
@@ -6271,7 +6252,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="665">
       <c r="A665" t="s">
         <v>189</v>
       </c>
@@ -6279,7 +6260,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="666">
       <c r="A666" t="s">
         <v>190</v>
       </c>
@@ -6287,7 +6268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="667">
       <c r="A667" t="s">
         <v>190</v>
       </c>
@@ -6295,7 +6276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="668">
       <c r="A668" t="s">
         <v>190</v>
       </c>
@@ -6303,7 +6284,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="669">
       <c r="A669" t="s">
         <v>190</v>
       </c>
@@ -6311,7 +6292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="670">
       <c r="A670" t="s">
         <v>191</v>
       </c>
@@ -6319,7 +6300,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="671">
       <c r="A671" t="s">
         <v>191</v>
       </c>
@@ -6327,7 +6308,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="672">
       <c r="A672" t="s">
         <v>191</v>
       </c>
@@ -6335,7 +6316,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="673">
       <c r="A673" t="s">
         <v>191</v>
       </c>
@@ -6343,7 +6324,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="674">
       <c r="A674" t="s">
         <v>192</v>
       </c>
@@ -6351,7 +6332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="675">
       <c r="A675" t="s">
         <v>192</v>
       </c>
@@ -6359,7 +6340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="676">
       <c r="A676" t="s">
         <v>192</v>
       </c>
@@ -6367,7 +6348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="677">
       <c r="A677" t="s">
         <v>192</v>
       </c>
@@ -6375,7 +6356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="678">
       <c r="A678" t="s">
         <v>193</v>
       </c>
@@ -6383,7 +6364,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="679">
       <c r="A679" t="s">
         <v>193</v>
       </c>
@@ -6391,7 +6372,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="680">
       <c r="A680" t="s">
         <v>193</v>
       </c>
@@ -6399,7 +6380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="681">
       <c r="A681" t="s">
         <v>193</v>
       </c>
@@ -6407,7 +6388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="682">
       <c r="A682" t="s">
         <v>194</v>
       </c>
@@ -6415,7 +6396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="683">
       <c r="A683" t="s">
         <v>194</v>
       </c>
@@ -6423,7 +6404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="684">
       <c r="A684" t="s">
         <v>194</v>
       </c>
@@ -6431,7 +6412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="685">
       <c r="A685" t="s">
         <v>194</v>
       </c>
@@ -6439,7 +6420,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="686">
       <c r="A686" t="s">
         <v>195</v>
       </c>
@@ -6447,7 +6428,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="687">
       <c r="A687" t="s">
         <v>195</v>
       </c>
@@ -6455,7 +6436,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="688">
       <c r="A688" t="s">
         <v>195</v>
       </c>
@@ -6463,7 +6444,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="689">
       <c r="A689" t="s">
         <v>195</v>
       </c>
@@ -6471,7 +6452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="690">
       <c r="A690" t="s">
         <v>196</v>
       </c>
@@ -6479,7 +6460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="691">
       <c r="A691" t="s">
         <v>196</v>
       </c>
@@ -6487,7 +6468,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="692">
       <c r="A692" t="s">
         <v>196</v>
       </c>
@@ -6495,7 +6476,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="693">
       <c r="A693" t="s">
         <v>196</v>
       </c>
@@ -6503,7 +6484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="694">
       <c r="A694" t="s">
         <v>197</v>
       </c>
@@ -6511,7 +6492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="695">
       <c r="A695" t="s">
         <v>197</v>
       </c>
@@ -6519,7 +6500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="696">
       <c r="A696" t="s">
         <v>197</v>
       </c>
@@ -6527,7 +6508,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="697">
       <c r="A697" t="s">
         <v>197</v>
       </c>
@@ -6535,7 +6516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="698">
       <c r="A698" t="s">
         <v>198</v>
       </c>
@@ -6543,7 +6524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="699">
       <c r="A699" t="s">
         <v>198</v>
       </c>
@@ -6551,7 +6532,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="700">
       <c r="A700" t="s">
         <v>198</v>
       </c>
@@ -6559,7 +6540,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="701">
       <c r="A701" t="s">
         <v>198</v>
       </c>
@@ -6567,7 +6548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="702">
       <c r="A702" t="s">
         <v>199</v>
       </c>
@@ -6575,7 +6556,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="703">
       <c r="A703" t="s">
         <v>199</v>
       </c>
@@ -6583,7 +6564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="704">
       <c r="A704" t="s">
         <v>199</v>
       </c>
@@ -6591,7 +6572,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="705">
       <c r="A705" t="s">
         <v>199</v>
       </c>
@@ -6601,6 +6582,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>